--- a/pools-example-large-teams-max-size.xlsx
+++ b/pools-example-large-teams-max-size.xlsx
@@ -1831,11 +1831,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3138,7 +3142,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3146,7 +3151,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3531,7 +3536,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -26205,7 +26210,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -26590,7 +26595,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-large-teams-max-size.xlsx
+++ b/pools-example-large-teams-max-size.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,17 +12,19 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
     <sheet name="Tree 3" sheetId="10" r:id="rId13"/>
     <sheet name="Tree 4" sheetId="11" r:id="rId14"/>
-    <sheet name="Tags" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print A" sheetId="12" r:id="rId15"/>
+    <sheet name="Names to Print B" sheetId="13" r:id="rId16"/>
+    <sheet name="Tags" sheetId="14" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$71</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$616</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$91</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$47</definedName>
+    <definedName localSheetId="10" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$44</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$527</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="409">
   <si>
     <t>Number of pools</t>
   </si>
@@ -1229,10 +1231,13 @@
     <t>Round 4 - Match 58</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
-  </si>
-  <si>
-    <t>Round 6 - Match 0</t>
+    <t>Round 5 - Match 59</t>
+  </si>
+  <si>
+    <t>Round 5 - Match 60</t>
+  </si>
+  <si>
+    <t>Round 6 - Match 61</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -3902,6 +3907,797 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D27</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D28</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D29</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D30</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D31</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D32</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D33</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D34</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D35</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D36</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D37</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D38</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D39</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D40</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D41</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D42</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D43</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D44</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D45</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D46</f>
+      </c>
+    </row>
+    <row r="45" ht="270" customHeight="true">
+      <c r="A45" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B45" s="27" t="str">
+        <f>data!D47</f>
+      </c>
+    </row>
+    <row r="46" ht="270" customHeight="true">
+      <c r="A46" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="B46" s="27" t="str">
+        <f>data!D48</f>
+      </c>
+    </row>
+    <row r="47" ht="270" customHeight="true">
+      <c r="A47" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B47" s="27" t="str">
+        <f>data!D49</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="15" manualBreakCount="15">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+    <brk id="45" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D50</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D51</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>297</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D52</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D53</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D54</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D55</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D56</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D57</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D58</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D59</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D60</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D61</f>
+      </c>
+    </row>
+    <row r="13" ht="270" customHeight="true">
+      <c r="A13" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f>data!D62</f>
+      </c>
+    </row>
+    <row r="14" ht="270" customHeight="true">
+      <c r="A14" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f>data!D63</f>
+      </c>
+    </row>
+    <row r="15" ht="270" customHeight="true">
+      <c r="A15" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f>data!D64</f>
+      </c>
+    </row>
+    <row r="16" ht="270" customHeight="true">
+      <c r="A16" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="B16" s="27" t="str">
+        <f>data!D65</f>
+      </c>
+    </row>
+    <row r="17" ht="270" customHeight="true">
+      <c r="A17" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f>data!D66</f>
+      </c>
+    </row>
+    <row r="18" ht="270" customHeight="true">
+      <c r="A18" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f>data!D67</f>
+      </c>
+    </row>
+    <row r="19" ht="270" customHeight="true">
+      <c r="A19" s="26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f>data!D68</f>
+      </c>
+    </row>
+    <row r="20" ht="270" customHeight="true">
+      <c r="A20" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f>data!D69</f>
+      </c>
+    </row>
+    <row r="21" ht="270" customHeight="true">
+      <c r="A21" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f>data!D70</f>
+      </c>
+    </row>
+    <row r="22" ht="270" customHeight="true">
+      <c r="A22" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f>data!D71</f>
+      </c>
+    </row>
+    <row r="23" ht="270" customHeight="true">
+      <c r="A23" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f>data!D72</f>
+      </c>
+    </row>
+    <row r="24" ht="270" customHeight="true">
+      <c r="A24" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f>data!D73</f>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="true">
+      <c r="A25" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f>data!D74</f>
+      </c>
+    </row>
+    <row r="26" ht="270" customHeight="true">
+      <c r="A26" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f>data!D75</f>
+      </c>
+    </row>
+    <row r="27" ht="270" customHeight="true">
+      <c r="A27" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f>data!D76</f>
+      </c>
+    </row>
+    <row r="28" ht="270" customHeight="true">
+      <c r="A28" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f>data!D77</f>
+      </c>
+    </row>
+    <row r="29" ht="270" customHeight="true">
+      <c r="A29" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f>data!D78</f>
+      </c>
+    </row>
+    <row r="30" ht="270" customHeight="true">
+      <c r="A30" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f>data!D79</f>
+      </c>
+    </row>
+    <row r="31" ht="270" customHeight="true">
+      <c r="A31" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f>data!D80</f>
+      </c>
+    </row>
+    <row r="32" ht="270" customHeight="true">
+      <c r="A32" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f>data!D81</f>
+      </c>
+    </row>
+    <row r="33" ht="270" customHeight="true">
+      <c r="A33" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f>data!D82</f>
+      </c>
+    </row>
+    <row r="34" ht="270" customHeight="true">
+      <c r="A34" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f>data!D83</f>
+      </c>
+    </row>
+    <row r="35" ht="270" customHeight="true">
+      <c r="A35" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f>data!D84</f>
+      </c>
+    </row>
+    <row r="36" ht="270" customHeight="true">
+      <c r="A36" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f>data!D85</f>
+      </c>
+    </row>
+    <row r="37" ht="270" customHeight="true">
+      <c r="A37" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f>data!D86</f>
+      </c>
+    </row>
+    <row r="38" ht="270" customHeight="true">
+      <c r="A38" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f>data!D87</f>
+      </c>
+    </row>
+    <row r="39" ht="270" customHeight="true">
+      <c r="A39" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="B39" s="27" t="str">
+        <f>data!D88</f>
+      </c>
+    </row>
+    <row r="40" ht="270" customHeight="true">
+      <c r="A40" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f>data!D89</f>
+      </c>
+    </row>
+    <row r="41" ht="270" customHeight="true">
+      <c r="A41" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f>data!D90</f>
+      </c>
+    </row>
+    <row r="42" ht="270" customHeight="true">
+      <c r="A42" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>data!D91</f>
+      </c>
+    </row>
+    <row r="43" ht="270" customHeight="true">
+      <c r="A43" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f>data!D92</f>
+      </c>
+    </row>
+    <row r="44" ht="270" customHeight="true">
+      <c r="A44" s="26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f>data!D93</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="14" manualBreakCount="14">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+    <brk id="15" max="16383" man="true"/>
+    <brk id="18" max="16383" man="true"/>
+    <brk id="21" max="16383" man="true"/>
+    <brk id="24" max="16383" man="true"/>
+    <brk id="27" max="16383" man="true"/>
+    <brk id="30" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
+    <brk id="36" max="16383" man="true"/>
+    <brk id="39" max="16383" man="true"/>
+    <brk id="42" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -5115,7 +5911,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -5126,7 +5922,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
@@ -5136,7 +5932,7 @@
     </row>
     <row r="15">
       <c r="E15" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
@@ -5146,7 +5942,7 @@
     </row>
     <row r="16">
       <c r="E16" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
@@ -5156,7 +5952,7 @@
     </row>
     <row r="17">
       <c r="E17" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -5166,7 +5962,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -5176,7 +5972,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -24937,7 +25733,7 @@
       <c r="F486" s="13"/>
       <c r="G486" s="13"/>
       <c r="I486" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J486" s="13"/>
       <c r="K486" s="13"/>
@@ -25196,7 +25992,7 @@
     </row>
     <row r="507">
       <c r="A507" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B507" s="13"/>
       <c r="C507" s="13"/>
@@ -25218,7 +26014,7 @@
     </row>
     <row r="509">
       <c r="A509" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O498)</f>
+        <f>CONCATENATE("M 60 ",O498)</f>
       </c>
       <c r="B509" s="14"/>
       <c r="C509" s="14"/>
@@ -25226,7 +26022,7 @@
       <c r="E509" s="14"/>
       <c r="F509" s="14"/>
       <c r="G509" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O498)</f>
+        <f>CONCATENATE("M 59 ",G498)</f>
       </c>
     </row>
     <row r="510">
@@ -25296,7 +26092,7 @@
     </row>
     <row r="516">
       <c r="A516" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O498)</f>
+        <f>CONCATENATE("M 60 ",O498)</f>
       </c>
       <c r="B516" s="14" t="s">
         <v>242</v>
@@ -25312,7 +26108,7 @@
         <v>242</v>
       </c>
       <c r="G516" s="14" t="str">
-        <f>CONCATENATE("M 0 ",O498)</f>
+        <f>CONCATENATE("M 59 ",G498)</f>
       </c>
     </row>
     <row r="517">
@@ -25431,781 +26227,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="27" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="26" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="25" ht="270" customHeight="true">
-      <c r="A25" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="B25" s="27" t="str">
-        <f>data!D27</f>
-      </c>
-    </row>
-    <row r="26" ht="270" customHeight="true">
-      <c r="A26" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="B26" s="27" t="str">
-        <f>data!D28</f>
-      </c>
-    </row>
-    <row r="27" ht="270" customHeight="true">
-      <c r="A27" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="B27" s="27" t="str">
-        <f>data!D29</f>
-      </c>
-    </row>
-    <row r="28" ht="270" customHeight="true">
-      <c r="A28" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="B28" s="27" t="str">
-        <f>data!D30</f>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="true">
-      <c r="A29" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="B29" s="27" t="str">
-        <f>data!D31</f>
-      </c>
-    </row>
-    <row r="30" ht="270" customHeight="true">
-      <c r="A30" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B30" s="27" t="str">
-        <f>data!D32</f>
-      </c>
-    </row>
-    <row r="31" ht="270" customHeight="true">
-      <c r="A31" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="B31" s="27" t="str">
-        <f>data!D33</f>
-      </c>
-    </row>
-    <row r="32" ht="270" customHeight="true">
-      <c r="A32" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="B32" s="27" t="str">
-        <f>data!D34</f>
-      </c>
-    </row>
-    <row r="33" ht="270" customHeight="true">
-      <c r="A33" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="B33" s="27" t="str">
-        <f>data!D35</f>
-      </c>
-    </row>
-    <row r="34" ht="270" customHeight="true">
-      <c r="A34" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="B34" s="27" t="str">
-        <f>data!D36</f>
-      </c>
-    </row>
-    <row r="35" ht="270" customHeight="true">
-      <c r="A35" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="B35" s="27" t="str">
-        <f>data!D37</f>
-      </c>
-    </row>
-    <row r="36" ht="270" customHeight="true">
-      <c r="A36" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="B36" s="27" t="str">
-        <f>data!D38</f>
-      </c>
-    </row>
-    <row r="37" ht="270" customHeight="true">
-      <c r="A37" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="B37" s="27" t="str">
-        <f>data!D39</f>
-      </c>
-    </row>
-    <row r="38" ht="270" customHeight="true">
-      <c r="A38" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="B38" s="27" t="str">
-        <f>data!D40</f>
-      </c>
-    </row>
-    <row r="39" ht="270" customHeight="true">
-      <c r="A39" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="B39" s="27" t="str">
-        <f>data!D41</f>
-      </c>
-    </row>
-    <row r="40" ht="270" customHeight="true">
-      <c r="A40" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="B40" s="27" t="str">
-        <f>data!D42</f>
-      </c>
-    </row>
-    <row r="41" ht="270" customHeight="true">
-      <c r="A41" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="B41" s="27" t="str">
-        <f>data!D43</f>
-      </c>
-    </row>
-    <row r="42" ht="270" customHeight="true">
-      <c r="A42" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="B42" s="27" t="str">
-        <f>data!D44</f>
-      </c>
-    </row>
-    <row r="43" ht="270" customHeight="true">
-      <c r="A43" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="27" t="str">
-        <f>data!D45</f>
-      </c>
-    </row>
-    <row r="44" ht="270" customHeight="true">
-      <c r="A44" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="B44" s="27" t="str">
-        <f>data!D46</f>
-      </c>
-    </row>
-    <row r="45" ht="270" customHeight="true">
-      <c r="A45" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="B45" s="27" t="str">
-        <f>data!D47</f>
-      </c>
-    </row>
-    <row r="46" ht="270" customHeight="true">
-      <c r="A46" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="B46" s="27" t="str">
-        <f>data!D48</f>
-      </c>
-    </row>
-    <row r="47" ht="270" customHeight="true">
-      <c r="A47" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="B47" s="27" t="str">
-        <f>data!D49</f>
-      </c>
-    </row>
-    <row r="48" ht="270" customHeight="true">
-      <c r="A48" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="B48" s="27" t="str">
-        <f>data!D50</f>
-      </c>
-    </row>
-    <row r="49" ht="270" customHeight="true">
-      <c r="A49" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="B49" s="27" t="str">
-        <f>data!D51</f>
-      </c>
-    </row>
-    <row r="50" ht="270" customHeight="true">
-      <c r="A50" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="B50" s="27" t="str">
-        <f>data!D52</f>
-      </c>
-    </row>
-    <row r="51" ht="270" customHeight="true">
-      <c r="A51" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="B51" s="27" t="str">
-        <f>data!D53</f>
-      </c>
-    </row>
-    <row r="52" ht="270" customHeight="true">
-      <c r="A52" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="B52" s="27" t="str">
-        <f>data!D54</f>
-      </c>
-    </row>
-    <row r="53" ht="270" customHeight="true">
-      <c r="A53" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B53" s="27" t="str">
-        <f>data!D55</f>
-      </c>
-    </row>
-    <row r="54" ht="270" customHeight="true">
-      <c r="A54" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="B54" s="27" t="str">
-        <f>data!D56</f>
-      </c>
-    </row>
-    <row r="55" ht="270" customHeight="true">
-      <c r="A55" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="B55" s="27" t="str">
-        <f>data!D57</f>
-      </c>
-    </row>
-    <row r="56" ht="270" customHeight="true">
-      <c r="A56" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="B56" s="27" t="str">
-        <f>data!D58</f>
-      </c>
-    </row>
-    <row r="57" ht="270" customHeight="true">
-      <c r="A57" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="B57" s="27" t="str">
-        <f>data!D59</f>
-      </c>
-    </row>
-    <row r="58" ht="270" customHeight="true">
-      <c r="A58" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="B58" s="27" t="str">
-        <f>data!D60</f>
-      </c>
-    </row>
-    <row r="59" ht="270" customHeight="true">
-      <c r="A59" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="B59" s="27" t="str">
-        <f>data!D61</f>
-      </c>
-    </row>
-    <row r="60" ht="270" customHeight="true">
-      <c r="A60" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="B60" s="27" t="str">
-        <f>data!D62</f>
-      </c>
-    </row>
-    <row r="61" ht="270" customHeight="true">
-      <c r="A61" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="B61" s="27" t="str">
-        <f>data!D63</f>
-      </c>
-    </row>
-    <row r="62" ht="270" customHeight="true">
-      <c r="A62" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="B62" s="27" t="str">
-        <f>data!D64</f>
-      </c>
-    </row>
-    <row r="63" ht="270" customHeight="true">
-      <c r="A63" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B63" s="27" t="str">
-        <f>data!D65</f>
-      </c>
-    </row>
-    <row r="64" ht="270" customHeight="true">
-      <c r="A64" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="B64" s="27" t="str">
-        <f>data!D66</f>
-      </c>
-    </row>
-    <row r="65" ht="270" customHeight="true">
-      <c r="A65" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="B65" s="27" t="str">
-        <f>data!D67</f>
-      </c>
-    </row>
-    <row r="66" ht="270" customHeight="true">
-      <c r="A66" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B66" s="27" t="str">
-        <f>data!D68</f>
-      </c>
-    </row>
-    <row r="67" ht="270" customHeight="true">
-      <c r="A67" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B67" s="27" t="str">
-        <f>data!D69</f>
-      </c>
-    </row>
-    <row r="68" ht="270" customHeight="true">
-      <c r="A68" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="B68" s="27" t="str">
-        <f>data!D70</f>
-      </c>
-    </row>
-    <row r="69" ht="270" customHeight="true">
-      <c r="A69" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="B69" s="27" t="str">
-        <f>data!D71</f>
-      </c>
-    </row>
-    <row r="70" ht="270" customHeight="true">
-      <c r="A70" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="B70" s="27" t="str">
-        <f>data!D72</f>
-      </c>
-    </row>
-    <row r="71" ht="270" customHeight="true">
-      <c r="A71" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="B71" s="27" t="str">
-        <f>data!D73</f>
-      </c>
-    </row>
-    <row r="72" ht="270" customHeight="true">
-      <c r="A72" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="B72" s="27" t="str">
-        <f>data!D74</f>
-      </c>
-    </row>
-    <row r="73" ht="270" customHeight="true">
-      <c r="A73" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="B73" s="27" t="str">
-        <f>data!D75</f>
-      </c>
-    </row>
-    <row r="74" ht="270" customHeight="true">
-      <c r="A74" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B74" s="27" t="str">
-        <f>data!D76</f>
-      </c>
-    </row>
-    <row r="75" ht="270" customHeight="true">
-      <c r="A75" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="B75" s="27" t="str">
-        <f>data!D77</f>
-      </c>
-    </row>
-    <row r="76" ht="270" customHeight="true">
-      <c r="A76" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="B76" s="27" t="str">
-        <f>data!D78</f>
-      </c>
-    </row>
-    <row r="77" ht="270" customHeight="true">
-      <c r="A77" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="B77" s="27" t="str">
-        <f>data!D79</f>
-      </c>
-    </row>
-    <row r="78" ht="270" customHeight="true">
-      <c r="A78" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="B78" s="27" t="str">
-        <f>data!D80</f>
-      </c>
-    </row>
-    <row r="79" ht="270" customHeight="true">
-      <c r="A79" s="26" t="s">
-        <v>326</v>
-      </c>
-      <c r="B79" s="27" t="str">
-        <f>data!D81</f>
-      </c>
-    </row>
-    <row r="80" ht="270" customHeight="true">
-      <c r="A80" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="B80" s="27" t="str">
-        <f>data!D82</f>
-      </c>
-    </row>
-    <row r="81" ht="270" customHeight="true">
-      <c r="A81" s="26" t="s">
-        <v>328</v>
-      </c>
-      <c r="B81" s="27" t="str">
-        <f>data!D83</f>
-      </c>
-    </row>
-    <row r="82" ht="270" customHeight="true">
-      <c r="A82" s="26" t="s">
-        <v>329</v>
-      </c>
-      <c r="B82" s="27" t="str">
-        <f>data!D84</f>
-      </c>
-    </row>
-    <row r="83" ht="270" customHeight="true">
-      <c r="A83" s="26" t="s">
-        <v>330</v>
-      </c>
-      <c r="B83" s="27" t="str">
-        <f>data!D85</f>
-      </c>
-    </row>
-    <row r="84" ht="270" customHeight="true">
-      <c r="A84" s="26" t="s">
-        <v>331</v>
-      </c>
-      <c r="B84" s="27" t="str">
-        <f>data!D86</f>
-      </c>
-    </row>
-    <row r="85" ht="270" customHeight="true">
-      <c r="A85" s="26" t="s">
-        <v>332</v>
-      </c>
-      <c r="B85" s="27" t="str">
-        <f>data!D87</f>
-      </c>
-    </row>
-    <row r="86" ht="270" customHeight="true">
-      <c r="A86" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="B86" s="27" t="str">
-        <f>data!D88</f>
-      </c>
-    </row>
-    <row r="87" ht="270" customHeight="true">
-      <c r="A87" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B87" s="27" t="str">
-        <f>data!D89</f>
-      </c>
-    </row>
-    <row r="88" ht="270" customHeight="true">
-      <c r="A88" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B88" s="27" t="str">
-        <f>data!D90</f>
-      </c>
-    </row>
-    <row r="89" ht="270" customHeight="true">
-      <c r="A89" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="B89" s="27" t="str">
-        <f>data!D91</f>
-      </c>
-    </row>
-    <row r="90" ht="270" customHeight="true">
-      <c r="A90" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="B90" s="27" t="str">
-        <f>data!D92</f>
-      </c>
-    </row>
-    <row r="91" ht="270" customHeight="true">
-      <c r="A91" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="B91" s="27" t="str">
-        <f>data!D93</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="30" manualBreakCount="30">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-    <brk id="27" max="16383" man="true"/>
-    <brk id="30" max="16383" man="true"/>
-    <brk id="33" max="16383" man="true"/>
-    <brk id="36" max="16383" man="true"/>
-    <brk id="39" max="16383" man="true"/>
-    <brk id="42" max="16383" man="true"/>
-    <brk id="45" max="16383" man="true"/>
-    <brk id="48" max="16383" man="true"/>
-    <brk id="51" max="16383" man="true"/>
-    <brk id="54" max="16383" man="true"/>
-    <brk id="57" max="16383" man="true"/>
-    <brk id="60" max="16383" man="true"/>
-    <brk id="63" max="16383" man="true"/>
-    <brk id="66" max="16383" man="true"/>
-    <brk id="69" max="16383" man="true"/>
-    <brk id="72" max="16383" man="true"/>
-    <brk id="75" max="16383" man="true"/>
-    <brk id="78" max="16383" man="true"/>
-    <brk id="81" max="16383" man="true"/>
-    <brk id="84" max="16383" man="true"/>
-    <brk id="87" max="16383" man="true"/>
-    <brk id="90" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-large-teams-max-size.xlsx
+++ b/pools-example-large-teams-max-size.xlsx
@@ -3233,7 +3233,7 @@
         <f>"2. " &amp; data!$B$51</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G83)</f>
       </c>
     </row>
     <row r="7">
@@ -3254,7 +3254,7 @@
         <f>'data'!$A$55</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G44)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G41)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3277,7 +3277,7 @@
         <f>"2. " &amp; data!$B$54</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G130)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G127)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3294,7 +3294,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G169)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3316,7 +3316,7 @@
         <f>"1. " &amp; data!$B$56</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G216)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G213)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3341,7 +3341,7 @@
         <f>"3. " &amp; data!$B$58</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G258)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G255)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3361,7 +3361,7 @@
         <f>'data'!$A$61</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G302)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G299)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3380,7 +3380,7 @@
         <f>"2. " &amp; data!$B$60</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G344)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G341)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3397,7 +3397,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G388)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G385)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3419,7 +3419,7 @@
         <f>"1. " &amp; data!$B$62</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G430)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G427)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3444,7 +3444,7 @@
         <f>"3. " &amp; data!$B$64</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G474)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G471)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3464,7 +3464,7 @@
         <f>'data'!$A$67</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G516)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G513)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3483,7 +3483,7 @@
         <f>"2. " &amp; data!$B$66</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G560)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G557)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3504,7 +3504,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G602)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G599)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3524,7 +3524,7 @@
         <f>"1. " &amp; data!$B$68</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G646)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G643)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -3614,7 +3614,7 @@
         <f>"1. " &amp; data!$B$74</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G669)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G667)</f>
       </c>
     </row>
     <row r="6">
@@ -3631,7 +3631,7 @@
         <f>"3. " &amp; data!$B$76</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O44)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O41)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -3649,7 +3649,7 @@
         <f>'data'!$A$79</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O83)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -3672,7 +3672,7 @@
         <f>"2. " &amp; data!$B$78</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O130)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O127)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -3689,7 +3689,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O169)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -3711,7 +3711,7 @@
         <f>"1. " &amp; data!$B$80</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O216)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O213)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -3736,7 +3736,7 @@
         <f>"3. " &amp; data!$B$82</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O258)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O255)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -3756,7 +3756,7 @@
         <f>'data'!$A$85</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O302)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O299)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -3775,7 +3775,7 @@
         <f>"2. " &amp; data!$B$84</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O344)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O341)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -3792,7 +3792,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O388)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O385)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -3814,7 +3814,7 @@
         <f>"1. " &amp; data!$B$86</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O430)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O427)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -3839,7 +3839,7 @@
         <f>"3. " &amp; data!$B$88</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O474)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O471)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -3859,7 +3859,7 @@
         <f>'data'!$A$91</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O516)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O513)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -3878,7 +3878,7 @@
         <f>"2. " &amp; data!$B$90</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O560)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O557)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -3899,7 +3899,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O602)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O599)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -3919,7 +3919,7 @@
         <f>"1. " &amp; data!$B$92</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O643)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O641)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -20782,7 +20782,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -20790,10 +20790,10 @@
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G129)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G126)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G130)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G127)</f>
       </c>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -20801,7 +20801,7 @@
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G44)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G41)</f>
       </c>
     </row>
     <row r="5">
@@ -20926,7 +20926,7 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="B11" s="14" t="s">
         <v>247</v>
@@ -20942,10 +20942,10 @@
         <v>247</v>
       </c>
       <c r="G11" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G129)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G126)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G130)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G127)</f>
       </c>
       <c r="J11" s="14" t="s">
         <v>247</v>
@@ -20961,7 +20961,7 @@
         <v>247</v>
       </c>
       <c r="O11" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G44)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G41)</f>
       </c>
     </row>
     <row r="12">
@@ -21066,7 +21066,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G173)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G170)</f>
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -21074,10 +21074,10 @@
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G215)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G212)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G216)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G213)</f>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
@@ -21085,7 +21085,7 @@
       <c r="M20" s="14"/>
       <c r="N20" s="14"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G169)</f>
       </c>
     </row>
     <row r="21">
@@ -21210,7 +21210,7 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G173)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G170)</f>
       </c>
       <c r="B27" s="14" t="s">
         <v>247</v>
@@ -21226,10 +21226,10 @@
         <v>247</v>
       </c>
       <c r="G27" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G215)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G212)</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G216)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!G213)</f>
       </c>
       <c r="J27" s="14" t="s">
         <v>247</v>
@@ -21245,7 +21245,7 @@
         <v>247</v>
       </c>
       <c r="O27" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G172)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G169)</f>
       </c>
     </row>
     <row r="28">
@@ -21350,7 +21350,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G259)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G256)</f>
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -21358,10 +21358,10 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G301)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G298)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G302)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G299)</f>
       </c>
       <c r="J36" s="14"/>
       <c r="K36" s="14"/>
@@ -21369,7 +21369,7 @@
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G258)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G255)</f>
       </c>
     </row>
     <row r="37">
@@ -21494,7 +21494,7 @@
     </row>
     <row r="43">
       <c r="A43" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G259)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G256)</f>
       </c>
       <c r="B43" s="14" t="s">
         <v>247</v>
@@ -21510,10 +21510,10 @@
         <v>247</v>
       </c>
       <c r="G43" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G301)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G298)</f>
       </c>
       <c r="I43" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G302)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!G299)</f>
       </c>
       <c r="J43" s="14" t="s">
         <v>247</v>
@@ -21529,7 +21529,7 @@
         <v>247</v>
       </c>
       <c r="O43" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G258)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!G255)</f>
       </c>
     </row>
     <row r="44">
@@ -21634,7 +21634,7 @@
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G345)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G342)</f>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -21642,10 +21642,10 @@
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
       <c r="G52" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G387)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G384)</f>
       </c>
       <c r="I52" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G388)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G385)</f>
       </c>
       <c r="J52" s="14"/>
       <c r="K52" s="14"/>
@@ -21653,7 +21653,7 @@
       <c r="M52" s="14"/>
       <c r="N52" s="14"/>
       <c r="O52" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G344)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G341)</f>
       </c>
     </row>
     <row r="53">
@@ -21778,7 +21778,7 @@
     </row>
     <row r="59">
       <c r="A59" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G345)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G342)</f>
       </c>
       <c r="B59" s="14" t="s">
         <v>247</v>
@@ -21794,10 +21794,10 @@
         <v>247</v>
       </c>
       <c r="G59" s="14" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G387)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G384)</f>
       </c>
       <c r="I59" s="14" t="str">
-        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G388)</f>
+        <f>CONCATENATE("Pool I-2nd ",'Pool Matches'!G385)</f>
       </c>
       <c r="J59" s="14" t="s">
         <v>247</v>
@@ -21813,7 +21813,7 @@
         <v>247</v>
       </c>
       <c r="O59" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G344)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!G341)</f>
       </c>
     </row>
     <row r="60">
@@ -21918,7 +21918,7 @@
     </row>
     <row r="68">
       <c r="A68" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G431)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G428)</f>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -21926,10 +21926,10 @@
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
       <c r="G68" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G473)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G470)</f>
       </c>
       <c r="I68" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G474)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G471)</f>
       </c>
       <c r="J68" s="14"/>
       <c r="K68" s="14"/>
@@ -21937,7 +21937,7 @@
       <c r="M68" s="14"/>
       <c r="N68" s="14"/>
       <c r="O68" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G430)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G427)</f>
       </c>
     </row>
     <row r="69">
@@ -22062,7 +22062,7 @@
     </row>
     <row r="75">
       <c r="A75" s="14" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G431)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G428)</f>
       </c>
       <c r="B75" s="14" t="s">
         <v>247</v>
@@ -22078,10 +22078,10 @@
         <v>247</v>
       </c>
       <c r="G75" s="14" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G473)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G470)</f>
       </c>
       <c r="I75" s="14" t="str">
-        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G474)</f>
+        <f>CONCATENATE("Pool K-2nd ",'Pool Matches'!G471)</f>
       </c>
       <c r="J75" s="14" t="s">
         <v>247</v>
@@ -22097,7 +22097,7 @@
         <v>247</v>
       </c>
       <c r="O75" s="14" t="str">
-        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G430)</f>
+        <f>CONCATENATE("Pool J-1st ",'Pool Matches'!G427)</f>
       </c>
     </row>
     <row r="76">
@@ -22202,7 +22202,7 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G517)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G514)</f>
       </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -22210,10 +22210,10 @@
       <c r="E84" s="14"/>
       <c r="F84" s="14"/>
       <c r="G84" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G559)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G556)</f>
       </c>
       <c r="I84" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G560)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G557)</f>
       </c>
       <c r="J84" s="14"/>
       <c r="K84" s="14"/>
@@ -22221,7 +22221,7 @@
       <c r="M84" s="14"/>
       <c r="N84" s="14"/>
       <c r="O84" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G516)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G513)</f>
       </c>
     </row>
     <row r="85">
@@ -22346,7 +22346,7 @@
     </row>
     <row r="91">
       <c r="A91" s="14" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G517)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G514)</f>
       </c>
       <c r="B91" s="14" t="s">
         <v>247</v>
@@ -22362,10 +22362,10 @@
         <v>247</v>
       </c>
       <c r="G91" s="14" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G559)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G556)</f>
       </c>
       <c r="I91" s="14" t="str">
-        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G560)</f>
+        <f>CONCATENATE("Pool M-2nd ",'Pool Matches'!G557)</f>
       </c>
       <c r="J91" s="14" t="s">
         <v>247</v>
@@ -22381,7 +22381,7 @@
         <v>247</v>
       </c>
       <c r="O91" s="14" t="str">
-        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G516)</f>
+        <f>CONCATENATE("Pool L-1st ",'Pool Matches'!G513)</f>
       </c>
     </row>
     <row r="92">
@@ -22486,7 +22486,7 @@
     </row>
     <row r="100">
       <c r="A100" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G603)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G600)</f>
       </c>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -22494,10 +22494,10 @@
       <c r="E100" s="14"/>
       <c r="F100" s="14"/>
       <c r="G100" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G645)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G642)</f>
       </c>
       <c r="I100" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G646)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G643)</f>
       </c>
       <c r="J100" s="14"/>
       <c r="K100" s="14"/>
@@ -22505,7 +22505,7 @@
       <c r="M100" s="14"/>
       <c r="N100" s="14"/>
       <c r="O100" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G602)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G599)</f>
       </c>
     </row>
     <row r="101">
@@ -22630,7 +22630,7 @@
     </row>
     <row r="107">
       <c r="A107" s="14" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G603)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G600)</f>
       </c>
       <c r="B107" s="14" t="s">
         <v>247</v>
@@ -22646,10 +22646,10 @@
         <v>247</v>
       </c>
       <c r="G107" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G645)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G642)</f>
       </c>
       <c r="I107" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G646)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G643)</f>
       </c>
       <c r="J107" s="14" t="s">
         <v>247</v>
@@ -22665,7 +22665,7 @@
         <v>247</v>
       </c>
       <c r="O107" s="14" t="str">
-        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G602)</f>
+        <f>CONCATENATE("Pool N-1st ",'Pool Matches'!G599)</f>
       </c>
     </row>
     <row r="108">
@@ -22770,7 +22770,7 @@
     </row>
     <row r="116">
       <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G670)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G668)</f>
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -22778,10 +22778,10 @@
       <c r="E116" s="14"/>
       <c r="F116" s="14"/>
       <c r="G116" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O40)</f>
       </c>
       <c r="I116" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O44)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O41)</f>
       </c>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
@@ -22789,7 +22789,7 @@
       <c r="M116" s="14"/>
       <c r="N116" s="14"/>
       <c r="O116" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G669)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G667)</f>
       </c>
     </row>
     <row r="117">
@@ -22914,7 +22914,7 @@
     </row>
     <row r="123">
       <c r="A123" s="14" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G670)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G668)</f>
       </c>
       <c r="B123" s="14" t="s">
         <v>247</v>
@@ -22930,10 +22930,10 @@
         <v>247</v>
       </c>
       <c r="G123" s="14" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O40)</f>
       </c>
       <c r="I123" s="14" t="str">
-        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O44)</f>
+        <f>CONCATENATE("Pool Q-2nd ",'Pool Matches'!O41)</f>
       </c>
       <c r="J123" s="14" t="s">
         <v>247</v>
@@ -22949,7 +22949,7 @@
         <v>247</v>
       </c>
       <c r="O123" s="14" t="str">
-        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G669)</f>
+        <f>CONCATENATE("Pool P-1st ",'Pool Matches'!G667)</f>
       </c>
     </row>
     <row r="124">
@@ -23054,7 +23054,7 @@
     </row>
     <row r="132">
       <c r="A132" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -23062,10 +23062,10 @@
       <c r="E132" s="14"/>
       <c r="F132" s="14"/>
       <c r="G132" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O129)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O126)</f>
       </c>
       <c r="I132" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O130)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O127)</f>
       </c>
       <c r="J132" s="14"/>
       <c r="K132" s="14"/>
@@ -23073,7 +23073,7 @@
       <c r="M132" s="14"/>
       <c r="N132" s="14"/>
       <c r="O132" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O83)</f>
       </c>
     </row>
     <row r="133">
@@ -23198,7 +23198,7 @@
     </row>
     <row r="139">
       <c r="A139" s="14" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="B139" s="14" t="s">
         <v>247</v>
@@ -23214,10 +23214,10 @@
         <v>247</v>
       </c>
       <c r="G139" s="14" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O129)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O126)</f>
       </c>
       <c r="I139" s="14" t="str">
-        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O130)</f>
+        <f>CONCATENATE("Pool S-2nd ",'Pool Matches'!O127)</f>
       </c>
       <c r="J139" s="14" t="s">
         <v>247</v>
@@ -23233,7 +23233,7 @@
         <v>247</v>
       </c>
       <c r="O139" s="14" t="str">
-        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O86)</f>
+        <f>CONCATENATE("Pool R-1st ",'Pool Matches'!O83)</f>
       </c>
     </row>
     <row r="140">
@@ -23338,7 +23338,7 @@
     </row>
     <row r="148">
       <c r="A148" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O173)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O170)</f>
       </c>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -23346,10 +23346,10 @@
       <c r="E148" s="14"/>
       <c r="F148" s="14"/>
       <c r="G148" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O215)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O212)</f>
       </c>
       <c r="I148" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O216)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O213)</f>
       </c>
       <c r="J148" s="14"/>
       <c r="K148" s="14"/>
@@ -23357,7 +23357,7 @@
       <c r="M148" s="14"/>
       <c r="N148" s="14"/>
       <c r="O148" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O169)</f>
       </c>
     </row>
     <row r="149">
@@ -23482,7 +23482,7 @@
     </row>
     <row r="155">
       <c r="A155" s="14" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O173)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O170)</f>
       </c>
       <c r="B155" s="14" t="s">
         <v>247</v>
@@ -23498,10 +23498,10 @@
         <v>247</v>
       </c>
       <c r="G155" s="14" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O215)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O212)</f>
       </c>
       <c r="I155" s="14" t="str">
-        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O216)</f>
+        <f>CONCATENATE("Pool U-2nd ",'Pool Matches'!O213)</f>
       </c>
       <c r="J155" s="14" t="s">
         <v>247</v>
@@ -23517,7 +23517,7 @@
         <v>247</v>
       </c>
       <c r="O155" s="14" t="str">
-        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O172)</f>
+        <f>CONCATENATE("Pool T-1st ",'Pool Matches'!O169)</f>
       </c>
     </row>
     <row r="156">
@@ -23622,7 +23622,7 @@
     </row>
     <row r="164">
       <c r="A164" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O259)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O256)</f>
       </c>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -23630,10 +23630,10 @@
       <c r="E164" s="14"/>
       <c r="F164" s="14"/>
       <c r="G164" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O301)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O298)</f>
       </c>
       <c r="I164" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O302)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O299)</f>
       </c>
       <c r="J164" s="14"/>
       <c r="K164" s="14"/>
@@ -23641,7 +23641,7 @@
       <c r="M164" s="14"/>
       <c r="N164" s="14"/>
       <c r="O164" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O258)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O255)</f>
       </c>
     </row>
     <row r="165">
@@ -23766,7 +23766,7 @@
     </row>
     <row r="171">
       <c r="A171" s="14" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O259)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O256)</f>
       </c>
       <c r="B171" s="14" t="s">
         <v>247</v>
@@ -23782,10 +23782,10 @@
         <v>247</v>
       </c>
       <c r="G171" s="14" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O301)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O298)</f>
       </c>
       <c r="I171" s="14" t="str">
-        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O302)</f>
+        <f>CONCATENATE("Pool W-2nd ",'Pool Matches'!O299)</f>
       </c>
       <c r="J171" s="14" t="s">
         <v>247</v>
@@ -23801,7 +23801,7 @@
         <v>247</v>
       </c>
       <c r="O171" s="14" t="str">
-        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O258)</f>
+        <f>CONCATENATE("Pool V-1st ",'Pool Matches'!O255)</f>
       </c>
     </row>
     <row r="172">
@@ -23906,7 +23906,7 @@
     </row>
     <row r="180">
       <c r="A180" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O345)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O342)</f>
       </c>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -23914,10 +23914,10 @@
       <c r="E180" s="14"/>
       <c r="F180" s="14"/>
       <c r="G180" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O387)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O384)</f>
       </c>
       <c r="I180" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O388)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O385)</f>
       </c>
       <c r="J180" s="14"/>
       <c r="K180" s="14"/>
@@ -23925,7 +23925,7 @@
       <c r="M180" s="14"/>
       <c r="N180" s="14"/>
       <c r="O180" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O344)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O341)</f>
       </c>
     </row>
     <row r="181">
@@ -24050,7 +24050,7 @@
     </row>
     <row r="187">
       <c r="A187" s="14" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O345)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O342)</f>
       </c>
       <c r="B187" s="14" t="s">
         <v>247</v>
@@ -24066,10 +24066,10 @@
         <v>247</v>
       </c>
       <c r="G187" s="14" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O387)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O384)</f>
       </c>
       <c r="I187" s="14" t="str">
-        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O388)</f>
+        <f>CONCATENATE("Pool Y-2nd ",'Pool Matches'!O385)</f>
       </c>
       <c r="J187" s="14" t="s">
         <v>247</v>
@@ -24085,7 +24085,7 @@
         <v>247</v>
       </c>
       <c r="O187" s="14" t="str">
-        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O344)</f>
+        <f>CONCATENATE("Pool X-1st ",'Pool Matches'!O341)</f>
       </c>
     </row>
     <row r="188">
@@ -24190,7 +24190,7 @@
     </row>
     <row r="196">
       <c r="A196" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O431)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O428)</f>
       </c>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -24198,10 +24198,10 @@
       <c r="E196" s="14"/>
       <c r="F196" s="14"/>
       <c r="G196" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O473)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O470)</f>
       </c>
       <c r="I196" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O474)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O471)</f>
       </c>
       <c r="J196" s="14"/>
       <c r="K196" s="14"/>
@@ -24209,7 +24209,7 @@
       <c r="M196" s="14"/>
       <c r="N196" s="14"/>
       <c r="O196" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O430)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O427)</f>
       </c>
     </row>
     <row r="197">
@@ -24334,7 +24334,7 @@
     </row>
     <row r="203">
       <c r="A203" s="14" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O431)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O428)</f>
       </c>
       <c r="B203" s="14" t="s">
         <v>247</v>
@@ -24350,10 +24350,10 @@
         <v>247</v>
       </c>
       <c r="G203" s="14" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O473)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O470)</f>
       </c>
       <c r="I203" s="14" t="str">
-        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O474)</f>
+        <f>CONCATENATE("Pool AA-2nd ",'Pool Matches'!O471)</f>
       </c>
       <c r="J203" s="14" t="s">
         <v>247</v>
@@ -24369,7 +24369,7 @@
         <v>247</v>
       </c>
       <c r="O203" s="14" t="str">
-        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O430)</f>
+        <f>CONCATENATE("Pool Z-1st ",'Pool Matches'!O427)</f>
       </c>
     </row>
     <row r="204">
@@ -24474,7 +24474,7 @@
     </row>
     <row r="212">
       <c r="A212" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O517)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O514)</f>
       </c>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -24482,10 +24482,10 @@
       <c r="E212" s="14"/>
       <c r="F212" s="14"/>
       <c r="G212" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O559)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O556)</f>
       </c>
       <c r="I212" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O560)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O557)</f>
       </c>
       <c r="J212" s="14"/>
       <c r="K212" s="14"/>
@@ -24493,7 +24493,7 @@
       <c r="M212" s="14"/>
       <c r="N212" s="14"/>
       <c r="O212" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O516)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O513)</f>
       </c>
     </row>
     <row r="213">
@@ -24618,7 +24618,7 @@
     </row>
     <row r="219">
       <c r="A219" s="14" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O517)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O514)</f>
       </c>
       <c r="B219" s="14" t="s">
         <v>247</v>
@@ -24634,10 +24634,10 @@
         <v>247</v>
       </c>
       <c r="G219" s="14" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O559)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O556)</f>
       </c>
       <c r="I219" s="14" t="str">
-        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O560)</f>
+        <f>CONCATENATE("Pool CC-2nd ",'Pool Matches'!O557)</f>
       </c>
       <c r="J219" s="14" t="s">
         <v>247</v>
@@ -24653,7 +24653,7 @@
         <v>247</v>
       </c>
       <c r="O219" s="14" t="str">
-        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O516)</f>
+        <f>CONCATENATE("Pool BB-1st ",'Pool Matches'!O513)</f>
       </c>
     </row>
     <row r="220">
@@ -24758,7 +24758,7 @@
     </row>
     <row r="228">
       <c r="A228" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O603)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O600)</f>
       </c>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -24766,10 +24766,10 @@
       <c r="E228" s="14"/>
       <c r="F228" s="14"/>
       <c r="G228" s="14" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O642)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O640)</f>
       </c>
       <c r="I228" s="14" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O643)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O641)</f>
       </c>
       <c r="J228" s="14"/>
       <c r="K228" s="14"/>
@@ -24777,7 +24777,7 @@
       <c r="M228" s="14"/>
       <c r="N228" s="14"/>
       <c r="O228" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O602)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O599)</f>
       </c>
     </row>
     <row r="229">
@@ -24902,7 +24902,7 @@
     </row>
     <row r="235">
       <c r="A235" s="14" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O603)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O600)</f>
       </c>
       <c r="B235" s="14" t="s">
         <v>247</v>
@@ -24918,10 +24918,10 @@
         <v>247</v>
       </c>
       <c r="G235" s="14" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O642)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O640)</f>
       </c>
       <c r="I235" s="14" t="str">
-        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O643)</f>
+        <f>CONCATENATE("Pool EE-2nd ",'Pool Matches'!O641)</f>
       </c>
       <c r="J235" s="14" t="s">
         <v>247</v>
@@ -24937,7 +24937,7 @@
         <v>247</v>
       </c>
       <c r="O235" s="14" t="str">
-        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O602)</f>
+        <f>CONCATENATE("Pool DD-1st ",'Pool Matches'!O599)</f>
       </c>
     </row>
     <row r="236">
@@ -25050,7 +25050,7 @@
       <c r="E249" s="14"/>
       <c r="F249" s="14"/>
       <c r="G249" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G40)</f>
       </c>
       <c r="I249" s="14" t="str">
         <f>CONCATENATE("M 16 ",O15)</f>
@@ -25061,7 +25061,7 @@
       <c r="M249" s="14"/>
       <c r="N249" s="14"/>
       <c r="O249" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G83)</f>
       </c>
     </row>
     <row r="250">
@@ -25202,7 +25202,7 @@
         <v>247</v>
       </c>
       <c r="G256" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G40)</f>
       </c>
       <c r="I256" s="14" t="str">
         <f>CONCATENATE("M 16 ",O15)</f>
@@ -25221,7 +25221,7 @@
         <v>247</v>
       </c>
       <c r="O256" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G86)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G83)</f>
       </c>
     </row>
     <row r="257">
@@ -29550,7 +29550,7 @@
         <f>"2. " &amp; data!$B$4</f>
       </c>
       <c r="E6" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G43)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G40)</f>
       </c>
     </row>
     <row r="7">
@@ -29571,7 +29571,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G129)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G126)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -29594,7 +29594,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G87)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G84)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -29611,7 +29611,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G215)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!G212)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -29633,7 +29633,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G173)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G170)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -29658,7 +29658,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G301)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!G298)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -29678,7 +29678,7 @@
         <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G259)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!G256)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -29697,7 +29697,7 @@
         <f>"2. " &amp; data!$B$13</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G387)</f>
+        <f>CONCATENATE("Pool I-1st ",'Pool Matches'!G384)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -29714,7 +29714,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G345)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!G342)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -29736,7 +29736,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G473)</f>
+        <f>CONCATENATE("Pool K-1st ",'Pool Matches'!G470)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -29761,7 +29761,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G431)</f>
+        <f>CONCATENATE("Pool J-2nd ",'Pool Matches'!G428)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -29781,7 +29781,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G559)</f>
+        <f>CONCATENATE("Pool M-1st ",'Pool Matches'!G556)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -29800,7 +29800,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G517)</f>
+        <f>CONCATENATE("Pool L-2nd ",'Pool Matches'!G514)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -29821,7 +29821,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G645)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G642)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -29841,7 +29841,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G603)</f>
+        <f>CONCATENATE("Pool N-2nd ",'Pool Matches'!G600)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>
@@ -29931,7 +29931,7 @@
         <f>"1. " &amp; data!$B$27</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O43)</f>
+        <f>CONCATENATE("Pool Q-1st ",'Pool Matches'!O40)</f>
       </c>
     </row>
     <row r="6">
@@ -29948,7 +29948,7 @@
         <f>"3. " &amp; data!$B$29</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G670)</f>
+        <f>CONCATENATE("Pool P-2nd ",'Pool Matches'!G668)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -29966,7 +29966,7 @@
         <f>'data'!$A$32</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O129)</f>
+        <f>CONCATENATE("Pool S-1st ",'Pool Matches'!O126)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -29989,7 +29989,7 @@
         <f>"2. " &amp; data!$B$31</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O87)</f>
+        <f>CONCATENATE("Pool R-2nd ",'Pool Matches'!O84)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -30006,7 +30006,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O215)</f>
+        <f>CONCATENATE("Pool U-1st ",'Pool Matches'!O212)</f>
       </c>
       <c r="I13" s="20"/>
       <c r="J13" s="22"/>
@@ -30028,7 +30028,7 @@
         <f>"1. " &amp; data!$B$33</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O173)</f>
+        <f>CONCATENATE("Pool T-2nd ",'Pool Matches'!O170)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -30053,7 +30053,7 @@
         <f>"3. " &amp; data!$B$35</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O301)</f>
+        <f>CONCATENATE("Pool W-1st ",'Pool Matches'!O298)</f>
       </c>
       <c r="G17" s="20"/>
       <c r="K17" s="20"/>
@@ -30073,7 +30073,7 @@
         <f>'data'!$A$38</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O259)</f>
+        <f>CONCATENATE("Pool V-2nd ",'Pool Matches'!O256)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -30092,7 +30092,7 @@
         <f>"2. " &amp; data!$B$37</f>
       </c>
       <c r="C21" s="23" t="str">
-        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O387)</f>
+        <f>CONCATENATE("Pool Y-1st ",'Pool Matches'!O384)</f>
       </c>
       <c r="K21" s="20"/>
     </row>
@@ -30109,7 +30109,7 @@
     <row r="23">
       <c r="A23" s="22"/>
       <c r="C23" s="23" t="str">
-        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O345)</f>
+        <f>CONCATENATE("Pool X-2nd ",'Pool Matches'!O342)</f>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="20"/>
@@ -30131,7 +30131,7 @@
         <f>"1. " &amp; data!$B$39</f>
       </c>
       <c r="C25" s="23" t="str">
-        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O473)</f>
+        <f>CONCATENATE("Pool AA-1st ",'Pool Matches'!O470)</f>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="22"/>
@@ -30156,7 +30156,7 @@
         <f>"3. " &amp; data!$B$41</f>
       </c>
       <c r="C27" s="23" t="str">
-        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O431)</f>
+        <f>CONCATENATE("Pool Z-2nd ",'Pool Matches'!O428)</f>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="20"/>
@@ -30176,7 +30176,7 @@
         <f>'data'!$A$44</f>
       </c>
       <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O559)</f>
+        <f>CONCATENATE("Pool CC-1st ",'Pool Matches'!O556)</f>
       </c>
       <c r="I29" s="20"/>
     </row>
@@ -30195,7 +30195,7 @@
         <f>"2. " &amp; data!$B$43</f>
       </c>
       <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O517)</f>
+        <f>CONCATENATE("Pool BB-2nd ",'Pool Matches'!O514)</f>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="20"/>
@@ -30216,7 +30216,7 @@
     <row r="33">
       <c r="A33" s="22"/>
       <c r="C33" s="23" t="str">
-        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O642)</f>
+        <f>CONCATENATE("Pool EE-1st ",'Pool Matches'!O640)</f>
       </c>
       <c r="G33" s="20"/>
     </row>
@@ -30236,7 +30236,7 @@
         <f>"1. " &amp; data!$B$45</f>
       </c>
       <c r="C35" s="23" t="str">
-        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O603)</f>
+        <f>CONCATENATE("Pool DD-2nd ",'Pool Matches'!O600)</f>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="20"/>

--- a/pools-example-large-teams-max-size.xlsx
+++ b/pools-example-large-teams-max-size.xlsx
@@ -7240,10 +7240,10 @@
         <f>RANK(AC29,$AC$29:$AC$31)+COUNTIF($AC$28:AC28,AC29)</f>
       </c>
       <c r="U29" t="str">
-        <f>=(B29*1000000000)-(C29*10000000)+(D29*100000)+(B34*1000)-(C34*100)+(D34*10)+(E34*1)-(F34*0.01)</f>
+        <f>(B29*1000000000)-(C29*10000000)+(D29*100000)+(B34*1000)-(C34*100)+(D34*10)+(E34*1)-(F34*0.01)</f>
       </c>
       <c r="AC29" t="str">
-        <f>=(J29*1000000000)-(K29*10000000)+(L29*100000)+(J34*1000)-(K34*100)+(L34*10)+(M34*1)-(N34*0.01)</f>
+        <f>(J29*1000000000)-(K29*10000000)+(L29*100000)+(J34*1000)-(K34*100)+(L34*10)+(M34*1)-(N34*0.01)</f>
       </c>
     </row>
     <row r="30">
@@ -7278,10 +7278,10 @@
         <f>RANK(AC30,$AC$29:$AC$31)+COUNTIF($AC$28:AC29,AC30)</f>
       </c>
       <c r="U30" t="str">
-        <f>=(B30*1000000000)-(C30*10000000)+(D30*100000)+(B35*1000)-(C35*100)+(D35*10)+(E35*1)-(F35*0.01)</f>
+        <f>(B30*1000000000)-(C30*10000000)+(D30*100000)+(B35*1000)-(C35*100)+(D35*10)+(E35*1)-(F35*0.01)</f>
       </c>
       <c r="AC30" t="str">
-        <f>=(J30*1000000000)-(K30*10000000)+(L30*100000)+(J35*1000)-(K35*100)+(L35*10)+(M35*1)-(N35*0.01)</f>
+        <f>(J30*1000000000)-(K30*10000000)+(L30*100000)+(J35*1000)-(K35*100)+(L35*10)+(M35*1)-(N35*0.01)</f>
       </c>
     </row>
     <row r="31">
@@ -7316,10 +7316,10 @@
         <f>RANK(AC31,$AC$29:$AC$31)+COUNTIF($AC$28:AC30,AC31)</f>
       </c>
       <c r="U31" t="str">
-        <f>=(B31*1000000000)-(C31*10000000)+(D31*100000)+(B36*1000)-(C36*100)+(D36*10)+(E36*1)-(F36*0.01)</f>
+        <f>(B31*1000000000)-(C31*10000000)+(D31*100000)+(B36*1000)-(C36*100)+(D36*10)+(E36*1)-(F36*0.01)</f>
       </c>
       <c r="AC31" t="str">
-        <f>=(J31*1000000000)-(K31*10000000)+(L31*100000)+(J36*1000)-(K36*100)+(L36*10)+(M36*1)-(N36*0.01)</f>
+        <f>(J31*1000000000)-(K31*10000000)+(L31*100000)+(J36*1000)-(K36*100)+(L36*10)+(M36*1)-(N36*0.01)</f>
       </c>
     </row>
     <row r="33">
@@ -8174,10 +8174,10 @@
         <f>RANK(AC72,$AC$72:$AC$74)+COUNTIF($AC$71:AC71,AC72)</f>
       </c>
       <c r="U72" t="str">
-        <f>=(B72*1000000000)-(C72*10000000)+(D72*100000)+(B77*1000)-(C77*100)+(D77*10)+(E77*1)-(F77*0.01)</f>
+        <f>(B72*1000000000)-(C72*10000000)+(D72*100000)+(B77*1000)-(C77*100)+(D77*10)+(E77*1)-(F77*0.01)</f>
       </c>
       <c r="AC72" t="str">
-        <f>=(J72*1000000000)-(K72*10000000)+(L72*100000)+(J77*1000)-(K77*100)+(L77*10)+(M77*1)-(N77*0.01)</f>
+        <f>(J72*1000000000)-(K72*10000000)+(L72*100000)+(J77*1000)-(K77*100)+(L77*10)+(M77*1)-(N77*0.01)</f>
       </c>
     </row>
     <row r="73">
@@ -8212,10 +8212,10 @@
         <f>RANK(AC73,$AC$72:$AC$74)+COUNTIF($AC$71:AC72,AC73)</f>
       </c>
       <c r="U73" t="str">
-        <f>=(B73*1000000000)-(C73*10000000)+(D73*100000)+(B78*1000)-(C78*100)+(D78*10)+(E78*1)-(F78*0.01)</f>
+        <f>(B73*1000000000)-(C73*10000000)+(D73*100000)+(B78*1000)-(C78*100)+(D78*10)+(E78*1)-(F78*0.01)</f>
       </c>
       <c r="AC73" t="str">
-        <f>=(J73*1000000000)-(K73*10000000)+(L73*100000)+(J78*1000)-(K78*100)+(L78*10)+(M78*1)-(N78*0.01)</f>
+        <f>(J73*1000000000)-(K73*10000000)+(L73*100000)+(J78*1000)-(K78*100)+(L78*10)+(M78*1)-(N78*0.01)</f>
       </c>
     </row>
     <row r="74">
@@ -8250,10 +8250,10 @@
         <f>RANK(AC74,$AC$72:$AC$74)+COUNTIF($AC$71:AC73,AC74)</f>
       </c>
       <c r="U74" t="str">
-        <f>=(B74*1000000000)-(C74*10000000)+(D74*100000)+(B79*1000)-(C79*100)+(D79*10)+(E79*1)-(F79*0.01)</f>
+        <f>(B74*1000000000)-(C74*10000000)+(D74*100000)+(B79*1000)-(C79*100)+(D79*10)+(E79*1)-(F79*0.01)</f>
       </c>
       <c r="AC74" t="str">
-        <f>=(J74*1000000000)-(K74*10000000)+(L74*100000)+(J79*1000)-(K79*100)+(L79*10)+(M79*1)-(N79*0.01)</f>
+        <f>(J74*1000000000)-(K74*10000000)+(L74*100000)+(J79*1000)-(K79*100)+(L79*10)+(M79*1)-(N79*0.01)</f>
       </c>
     </row>
     <row r="76">
@@ -9108,10 +9108,10 @@
         <f>RANK(AC115,$AC$115:$AC$117)+COUNTIF($AC$114:AC114,AC115)</f>
       </c>
       <c r="U115" t="str">
-        <f>=(B115*1000000000)-(C115*10000000)+(D115*100000)+(B120*1000)-(C120*100)+(D120*10)+(E120*1)-(F120*0.01)</f>
+        <f>(B115*1000000000)-(C115*10000000)+(D115*100000)+(B120*1000)-(C120*100)+(D120*10)+(E120*1)-(F120*0.01)</f>
       </c>
       <c r="AC115" t="str">
-        <f>=(J115*1000000000)-(K115*10000000)+(L115*100000)+(J120*1000)-(K120*100)+(L120*10)+(M120*1)-(N120*0.01)</f>
+        <f>(J115*1000000000)-(K115*10000000)+(L115*100000)+(J120*1000)-(K120*100)+(L120*10)+(M120*1)-(N120*0.01)</f>
       </c>
     </row>
     <row r="116">
@@ -9146,10 +9146,10 @@
         <f>RANK(AC116,$AC$115:$AC$117)+COUNTIF($AC$114:AC115,AC116)</f>
       </c>
       <c r="U116" t="str">
-        <f>=(B116*1000000000)-(C116*10000000)+(D116*100000)+(B121*1000)-(C121*100)+(D121*10)+(E121*1)-(F121*0.01)</f>
+        <f>(B116*1000000000)-(C116*10000000)+(D116*100000)+(B121*1000)-(C121*100)+(D121*10)+(E121*1)-(F121*0.01)</f>
       </c>
       <c r="AC116" t="str">
-        <f>=(J116*1000000000)-(K116*10000000)+(L116*100000)+(J121*1000)-(K121*100)+(L121*10)+(M121*1)-(N121*0.01)</f>
+        <f>(J116*1000000000)-(K116*10000000)+(L116*100000)+(J121*1000)-(K121*100)+(L121*10)+(M121*1)-(N121*0.01)</f>
       </c>
     </row>
     <row r="117">
@@ -9184,10 +9184,10 @@
         <f>RANK(AC117,$AC$115:$AC$117)+COUNTIF($AC$114:AC116,AC117)</f>
       </c>
       <c r="U117" t="str">
-        <f>=(B117*1000000000)-(C117*10000000)+(D117*100000)+(B122*1000)-(C122*100)+(D122*10)+(E122*1)-(F122*0.01)</f>
+        <f>(B117*1000000000)-(C117*10000000)+(D117*100000)+(B122*1000)-(C122*100)+(D122*10)+(E122*1)-(F122*0.01)</f>
       </c>
       <c r="AC117" t="str">
-        <f>=(J117*1000000000)-(K117*10000000)+(L117*100000)+(J122*1000)-(K122*100)+(L122*10)+(M122*1)-(N122*0.01)</f>
+        <f>(J117*1000000000)-(K117*10000000)+(L117*100000)+(J122*1000)-(K122*100)+(L122*10)+(M122*1)-(N122*0.01)</f>
       </c>
     </row>
     <row r="119">
@@ -10042,10 +10042,10 @@
         <f>RANK(AC158,$AC$158:$AC$160)+COUNTIF($AC$157:AC157,AC158)</f>
       </c>
       <c r="U158" t="str">
-        <f>=(B158*1000000000)-(C158*10000000)+(D158*100000)+(B163*1000)-(C163*100)+(D163*10)+(E163*1)-(F163*0.01)</f>
+        <f>(B158*1000000000)-(C158*10000000)+(D158*100000)+(B163*1000)-(C163*100)+(D163*10)+(E163*1)-(F163*0.01)</f>
       </c>
       <c r="AC158" t="str">
-        <f>=(J158*1000000000)-(K158*10000000)+(L158*100000)+(J163*1000)-(K163*100)+(L163*10)+(M163*1)-(N163*0.01)</f>
+        <f>(J158*1000000000)-(K158*10000000)+(L158*100000)+(J163*1000)-(K163*100)+(L163*10)+(M163*1)-(N163*0.01)</f>
       </c>
     </row>
     <row r="159">
@@ -10080,10 +10080,10 @@
         <f>RANK(AC159,$AC$158:$AC$160)+COUNTIF($AC$157:AC158,AC159)</f>
       </c>
       <c r="U159" t="str">
-        <f>=(B159*1000000000)-(C159*10000000)+(D159*100000)+(B164*1000)-(C164*100)+(D164*10)+(E164*1)-(F164*0.01)</f>
+        <f>(B159*1000000000)-(C159*10000000)+(D159*100000)+(B164*1000)-(C164*100)+(D164*10)+(E164*1)-(F164*0.01)</f>
       </c>
       <c r="AC159" t="str">
-        <f>=(J159*1000000000)-(K159*10000000)+(L159*100000)+(J164*1000)-(K164*100)+(L164*10)+(M164*1)-(N164*0.01)</f>
+        <f>(J159*1000000000)-(K159*10000000)+(L159*100000)+(J164*1000)-(K164*100)+(L164*10)+(M164*1)-(N164*0.01)</f>
       </c>
     </row>
     <row r="160">
@@ -10118,10 +10118,10 @@
         <f>RANK(AC160,$AC$158:$AC$160)+COUNTIF($AC$157:AC159,AC160)</f>
       </c>
       <c r="U160" t="str">
-        <f>=(B160*1000000000)-(C160*10000000)+(D160*100000)+(B165*1000)-(C165*100)+(D165*10)+(E165*1)-(F165*0.01)</f>
+        <f>(B160*1000000000)-(C160*10000000)+(D160*100000)+(B165*1000)-(C165*100)+(D165*10)+(E165*1)-(F165*0.01)</f>
       </c>
       <c r="AC160" t="str">
-        <f>=(J160*1000000000)-(K160*10000000)+(L160*100000)+(J165*1000)-(K165*100)+(L165*10)+(M165*1)-(N165*0.01)</f>
+        <f>(J160*1000000000)-(K160*10000000)+(L160*100000)+(J165*1000)-(K165*100)+(L165*10)+(M165*1)-(N165*0.01)</f>
       </c>
     </row>
     <row r="162">
@@ -10976,10 +10976,10 @@
         <f>RANK(AC201,$AC$201:$AC$203)+COUNTIF($AC$200:AC200,AC201)</f>
       </c>
       <c r="U201" t="str">
-        <f>=(B201*1000000000)-(C201*10000000)+(D201*100000)+(B206*1000)-(C206*100)+(D206*10)+(E206*1)-(F206*0.01)</f>
+        <f>(B201*1000000000)-(C201*10000000)+(D201*100000)+(B206*1000)-(C206*100)+(D206*10)+(E206*1)-(F206*0.01)</f>
       </c>
       <c r="AC201" t="str">
-        <f>=(J201*1000000000)-(K201*10000000)+(L201*100000)+(J206*1000)-(K206*100)+(L206*10)+(M206*1)-(N206*0.01)</f>
+        <f>(J201*1000000000)-(K201*10000000)+(L201*100000)+(J206*1000)-(K206*100)+(L206*10)+(M206*1)-(N206*0.01)</f>
       </c>
     </row>
     <row r="202">
@@ -11014,10 +11014,10 @@
         <f>RANK(AC202,$AC$201:$AC$203)+COUNTIF($AC$200:AC201,AC202)</f>
       </c>
       <c r="U202" t="str">
-        <f>=(B202*1000000000)-(C202*10000000)+(D202*100000)+(B207*1000)-(C207*100)+(D207*10)+(E207*1)-(F207*0.01)</f>
+        <f>(B202*1000000000)-(C202*10000000)+(D202*100000)+(B207*1000)-(C207*100)+(D207*10)+(E207*1)-(F207*0.01)</f>
       </c>
       <c r="AC202" t="str">
-        <f>=(J202*1000000000)-(K202*10000000)+(L202*100000)+(J207*1000)-(K207*100)+(L207*10)+(M207*1)-(N207*0.01)</f>
+        <f>(J202*1000000000)-(K202*10000000)+(L202*100000)+(J207*1000)-(K207*100)+(L207*10)+(M207*1)-(N207*0.01)</f>
       </c>
     </row>
     <row r="203">
@@ -11052,10 +11052,10 @@
         <f>RANK(AC203,$AC$201:$AC$203)+COUNTIF($AC$200:AC202,AC203)</f>
       </c>
       <c r="U203" t="str">
-        <f>=(B203*1000000000)-(C203*10000000)+(D203*100000)+(B208*1000)-(C208*100)+(D208*10)+(E208*1)-(F208*0.01)</f>
+        <f>(B203*1000000000)-(C203*10000000)+(D203*100000)+(B208*1000)-(C208*100)+(D208*10)+(E208*1)-(F208*0.01)</f>
       </c>
       <c r="AC203" t="str">
-        <f>=(J203*1000000000)-(K203*10000000)+(L203*100000)+(J208*1000)-(K208*100)+(L208*10)+(M208*1)-(N208*0.01)</f>
+        <f>(J203*1000000000)-(K203*10000000)+(L203*100000)+(J208*1000)-(K208*100)+(L208*10)+(M208*1)-(N208*0.01)</f>
       </c>
     </row>
     <row r="205">
@@ -11910,10 +11910,10 @@
         <f>RANK(AC244,$AC$244:$AC$246)+COUNTIF($AC$243:AC243,AC244)</f>
       </c>
       <c r="U244" t="str">
-        <f>=(B244*1000000000)-(C244*10000000)+(D244*100000)+(B249*1000)-(C249*100)+(D249*10)+(E249*1)-(F249*0.01)</f>
+        <f>(B244*1000000000)-(C244*10000000)+(D244*100000)+(B249*1000)-(C249*100)+(D249*10)+(E249*1)-(F249*0.01)</f>
       </c>
       <c r="AC244" t="str">
-        <f>=(J244*1000000000)-(K244*10000000)+(L244*100000)+(J249*1000)-(K249*100)+(L249*10)+(M249*1)-(N249*0.01)</f>
+        <f>(J244*1000000000)-(K244*10000000)+(L244*100000)+(J249*1000)-(K249*100)+(L249*10)+(M249*1)-(N249*0.01)</f>
       </c>
     </row>
     <row r="245">
@@ -11948,10 +11948,10 @@
         <f>RANK(AC245,$AC$244:$AC$246)+COUNTIF($AC$243:AC244,AC245)</f>
       </c>
       <c r="U245" t="str">
-        <f>=(B245*1000000000)-(C245*10000000)+(D245*100000)+(B250*1000)-(C250*100)+(D250*10)+(E250*1)-(F250*0.01)</f>
+        <f>(B245*1000000000)-(C245*10000000)+(D245*100000)+(B250*1000)-(C250*100)+(D250*10)+(E250*1)-(F250*0.01)</f>
       </c>
       <c r="AC245" t="str">
-        <f>=(J245*1000000000)-(K245*10000000)+(L245*100000)+(J250*1000)-(K250*100)+(L250*10)+(M250*1)-(N250*0.01)</f>
+        <f>(J245*1000000000)-(K245*10000000)+(L245*100000)+(J250*1000)-(K250*100)+(L250*10)+(M250*1)-(N250*0.01)</f>
       </c>
     </row>
     <row r="246">
@@ -11986,10 +11986,10 @@
         <f>RANK(AC246,$AC$244:$AC$246)+COUNTIF($AC$243:AC245,AC246)</f>
       </c>
       <c r="U246" t="str">
-        <f>=(B246*1000000000)-(C246*10000000)+(D246*100000)+(B251*1000)-(C251*100)+(D251*10)+(E251*1)-(F251*0.01)</f>
+        <f>(B246*1000000000)-(C246*10000000)+(D246*100000)+(B251*1000)-(C251*100)+(D251*10)+(E251*1)-(F251*0.01)</f>
       </c>
       <c r="AC246" t="str">
-        <f>=(J246*1000000000)-(K246*10000000)+(L246*100000)+(J251*1000)-(K251*100)+(L251*10)+(M251*1)-(N251*0.01)</f>
+        <f>(J246*1000000000)-(K246*10000000)+(L246*100000)+(J251*1000)-(K251*100)+(L251*10)+(M251*1)-(N251*0.01)</f>
       </c>
     </row>
     <row r="248">
@@ -12844,10 +12844,10 @@
         <f>RANK(AC287,$AC$287:$AC$289)+COUNTIF($AC$286:AC286,AC287)</f>
       </c>
       <c r="U287" t="str">
-        <f>=(B287*1000000000)-(C287*10000000)+(D287*100000)+(B292*1000)-(C292*100)+(D292*10)+(E292*1)-(F292*0.01)</f>
+        <f>(B287*1000000000)-(C287*10000000)+(D287*100000)+(B292*1000)-(C292*100)+(D292*10)+(E292*1)-(F292*0.01)</f>
       </c>
       <c r="AC287" t="str">
-        <f>=(J287*1000000000)-(K287*10000000)+(L287*100000)+(J292*1000)-(K292*100)+(L292*10)+(M292*1)-(N292*0.01)</f>
+        <f>(J287*1000000000)-(K287*10000000)+(L287*100000)+(J292*1000)-(K292*100)+(L292*10)+(M292*1)-(N292*0.01)</f>
       </c>
     </row>
     <row r="288">
@@ -12882,10 +12882,10 @@
         <f>RANK(AC288,$AC$287:$AC$289)+COUNTIF($AC$286:AC287,AC288)</f>
       </c>
       <c r="U288" t="str">
-        <f>=(B288*1000000000)-(C288*10000000)+(D288*100000)+(B293*1000)-(C293*100)+(D293*10)+(E293*1)-(F293*0.01)</f>
+        <f>(B288*1000000000)-(C288*10000000)+(D288*100000)+(B293*1000)-(C293*100)+(D293*10)+(E293*1)-(F293*0.01)</f>
       </c>
       <c r="AC288" t="str">
-        <f>=(J288*1000000000)-(K288*10000000)+(L288*100000)+(J293*1000)-(K293*100)+(L293*10)+(M293*1)-(N293*0.01)</f>
+        <f>(J288*1000000000)-(K288*10000000)+(L288*100000)+(J293*1000)-(K293*100)+(L293*10)+(M293*1)-(N293*0.01)</f>
       </c>
     </row>
     <row r="289">
@@ -12920,10 +12920,10 @@
         <f>RANK(AC289,$AC$287:$AC$289)+COUNTIF($AC$286:AC288,AC289)</f>
       </c>
       <c r="U289" t="str">
-        <f>=(B289*1000000000)-(C289*10000000)+(D289*100000)+(B294*1000)-(C294*100)+(D294*10)+(E294*1)-(F294*0.01)</f>
+        <f>(B289*1000000000)-(C289*10000000)+(D289*100000)+(B294*1000)-(C294*100)+(D294*10)+(E294*1)-(F294*0.01)</f>
       </c>
       <c r="AC289" t="str">
-        <f>=(J289*1000000000)-(K289*10000000)+(L289*100000)+(J294*1000)-(K294*100)+(L294*10)+(M294*1)-(N294*0.01)</f>
+        <f>(J289*1000000000)-(K289*10000000)+(L289*100000)+(J294*1000)-(K294*100)+(L294*10)+(M294*1)-(N294*0.01)</f>
       </c>
     </row>
     <row r="291">
@@ -13778,10 +13778,10 @@
         <f>RANK(AC330,$AC$330:$AC$332)+COUNTIF($AC$329:AC329,AC330)</f>
       </c>
       <c r="U330" t="str">
-        <f>=(B330*1000000000)-(C330*10000000)+(D330*100000)+(B335*1000)-(C335*100)+(D335*10)+(E335*1)-(F335*0.01)</f>
+        <f>(B330*1000000000)-(C330*10000000)+(D330*100000)+(B335*1000)-(C335*100)+(D335*10)+(E335*1)-(F335*0.01)</f>
       </c>
       <c r="AC330" t="str">
-        <f>=(J330*1000000000)-(K330*10000000)+(L330*100000)+(J335*1000)-(K335*100)+(L335*10)+(M335*1)-(N335*0.01)</f>
+        <f>(J330*1000000000)-(K330*10000000)+(L330*100000)+(J335*1000)-(K335*100)+(L335*10)+(M335*1)-(N335*0.01)</f>
       </c>
     </row>
     <row r="331">
@@ -13816,10 +13816,10 @@
         <f>RANK(AC331,$AC$330:$AC$332)+COUNTIF($AC$329:AC330,AC331)</f>
       </c>
       <c r="U331" t="str">
-        <f>=(B331*1000000000)-(C331*10000000)+(D331*100000)+(B336*1000)-(C336*100)+(D336*10)+(E336*1)-(F336*0.01)</f>
+        <f>(B331*1000000000)-(C331*10000000)+(D331*100000)+(B336*1000)-(C336*100)+(D336*10)+(E336*1)-(F336*0.01)</f>
       </c>
       <c r="AC331" t="str">
-        <f>=(J331*1000000000)-(K331*10000000)+(L331*100000)+(J336*1000)-(K336*100)+(L336*10)+(M336*1)-(N336*0.01)</f>
+        <f>(J331*1000000000)-(K331*10000000)+(L331*100000)+(J336*1000)-(K336*100)+(L336*10)+(M336*1)-(N336*0.01)</f>
       </c>
     </row>
     <row r="332">
@@ -13854,10 +13854,10 @@
         <f>RANK(AC332,$AC$330:$AC$332)+COUNTIF($AC$329:AC331,AC332)</f>
       </c>
       <c r="U332" t="str">
-        <f>=(B332*1000000000)-(C332*10000000)+(D332*100000)+(B337*1000)-(C337*100)+(D337*10)+(E337*1)-(F337*0.01)</f>
+        <f>(B332*1000000000)-(C332*10000000)+(D332*100000)+(B337*1000)-(C337*100)+(D337*10)+(E337*1)-(F337*0.01)</f>
       </c>
       <c r="AC332" t="str">
-        <f>=(J332*1000000000)-(K332*10000000)+(L332*100000)+(J337*1000)-(K337*100)+(L337*10)+(M337*1)-(N337*0.01)</f>
+        <f>(J332*1000000000)-(K332*10000000)+(L332*100000)+(J337*1000)-(K337*100)+(L337*10)+(M337*1)-(N337*0.01)</f>
       </c>
     </row>
     <row r="334">
@@ -14712,10 +14712,10 @@
         <f>RANK(AC373,$AC$373:$AC$375)+COUNTIF($AC$372:AC372,AC373)</f>
       </c>
       <c r="U373" t="str">
-        <f>=(B373*1000000000)-(C373*10000000)+(D373*100000)+(B378*1000)-(C378*100)+(D378*10)+(E378*1)-(F378*0.01)</f>
+        <f>(B373*1000000000)-(C373*10000000)+(D373*100000)+(B378*1000)-(C378*100)+(D378*10)+(E378*1)-(F378*0.01)</f>
       </c>
       <c r="AC373" t="str">
-        <f>=(J373*1000000000)-(K373*10000000)+(L373*100000)+(J378*1000)-(K378*100)+(L378*10)+(M378*1)-(N378*0.01)</f>
+        <f>(J373*1000000000)-(K373*10000000)+(L373*100000)+(J378*1000)-(K378*100)+(L378*10)+(M378*1)-(N378*0.01)</f>
       </c>
     </row>
     <row r="374">
@@ -14750,10 +14750,10 @@
         <f>RANK(AC374,$AC$373:$AC$375)+COUNTIF($AC$372:AC373,AC374)</f>
       </c>
       <c r="U374" t="str">
-        <f>=(B374*1000000000)-(C374*10000000)+(D374*100000)+(B379*1000)-(C379*100)+(D379*10)+(E379*1)-(F379*0.01)</f>
+        <f>(B374*1000000000)-(C374*10000000)+(D374*100000)+(B379*1000)-(C379*100)+(D379*10)+(E379*1)-(F379*0.01)</f>
       </c>
       <c r="AC374" t="str">
-        <f>=(J374*1000000000)-(K374*10000000)+(L374*100000)+(J379*1000)-(K379*100)+(L379*10)+(M379*1)-(N379*0.01)</f>
+        <f>(J374*1000000000)-(K374*10000000)+(L374*100000)+(J379*1000)-(K379*100)+(L379*10)+(M379*1)-(N379*0.01)</f>
       </c>
     </row>
     <row r="375">
@@ -14788,10 +14788,10 @@
         <f>RANK(AC375,$AC$373:$AC$375)+COUNTIF($AC$372:AC374,AC375)</f>
       </c>
       <c r="U375" t="str">
-        <f>=(B375*1000000000)-(C375*10000000)+(D375*100000)+(B380*1000)-(C380*100)+(D380*10)+(E380*1)-(F380*0.01)</f>
+        <f>(B375*1000000000)-(C375*10000000)+(D375*100000)+(B380*1000)-(C380*100)+(D380*10)+(E380*1)-(F380*0.01)</f>
       </c>
       <c r="AC375" t="str">
-        <f>=(J375*1000000000)-(K375*10000000)+(L375*100000)+(J380*1000)-(K380*100)+(L380*10)+(M380*1)-(N380*0.01)</f>
+        <f>(J375*1000000000)-(K375*10000000)+(L375*100000)+(J380*1000)-(K380*100)+(L380*10)+(M380*1)-(N380*0.01)</f>
       </c>
     </row>
     <row r="377">
@@ -15646,10 +15646,10 @@
         <f>RANK(AC416,$AC$416:$AC$418)+COUNTIF($AC$415:AC415,AC416)</f>
       </c>
       <c r="U416" t="str">
-        <f>=(B416*1000000000)-(C416*10000000)+(D416*100000)+(B421*1000)-(C421*100)+(D421*10)+(E421*1)-(F421*0.01)</f>
+        <f>(B416*1000000000)-(C416*10000000)+(D416*100000)+(B421*1000)-(C421*100)+(D421*10)+(E421*1)-(F421*0.01)</f>
       </c>
       <c r="AC416" t="str">
-        <f>=(J416*1000000000)-(K416*10000000)+(L416*100000)+(J421*1000)-(K421*100)+(L421*10)+(M421*1)-(N421*0.01)</f>
+        <f>(J416*1000000000)-(K416*10000000)+(L416*100000)+(J421*1000)-(K421*100)+(L421*10)+(M421*1)-(N421*0.01)</f>
       </c>
     </row>
     <row r="417">
@@ -15684,10 +15684,10 @@
         <f>RANK(AC417,$AC$416:$AC$418)+COUNTIF($AC$415:AC416,AC417)</f>
       </c>
       <c r="U417" t="str">
-        <f>=(B417*1000000000)-(C417*10000000)+(D417*100000)+(B422*1000)-(C422*100)+(D422*10)+(E422*1)-(F422*0.01)</f>
+        <f>(B417*1000000000)-(C417*10000000)+(D417*100000)+(B422*1000)-(C422*100)+(D422*10)+(E422*1)-(F422*0.01)</f>
       </c>
       <c r="AC417" t="str">
-        <f>=(J417*1000000000)-(K417*10000000)+(L417*100000)+(J422*1000)-(K422*100)+(L422*10)+(M422*1)-(N422*0.01)</f>
+        <f>(J417*1000000000)-(K417*10000000)+(L417*100000)+(J422*1000)-(K422*100)+(L422*10)+(M422*1)-(N422*0.01)</f>
       </c>
     </row>
     <row r="418">
@@ -15722,10 +15722,10 @@
         <f>RANK(AC418,$AC$416:$AC$418)+COUNTIF($AC$415:AC417,AC418)</f>
       </c>
       <c r="U418" t="str">
-        <f>=(B418*1000000000)-(C418*10000000)+(D418*100000)+(B423*1000)-(C423*100)+(D423*10)+(E423*1)-(F423*0.01)</f>
+        <f>(B418*1000000000)-(C418*10000000)+(D418*100000)+(B423*1000)-(C423*100)+(D423*10)+(E423*1)-(F423*0.01)</f>
       </c>
       <c r="AC418" t="str">
-        <f>=(J418*1000000000)-(K418*10000000)+(L418*100000)+(J423*1000)-(K423*100)+(L423*10)+(M423*1)-(N423*0.01)</f>
+        <f>(J418*1000000000)-(K418*10000000)+(L418*100000)+(J423*1000)-(K423*100)+(L423*10)+(M423*1)-(N423*0.01)</f>
       </c>
     </row>
     <row r="420">
@@ -16580,10 +16580,10 @@
         <f>RANK(AC459,$AC$459:$AC$461)+COUNTIF($AC$458:AC458,AC459)</f>
       </c>
       <c r="U459" t="str">
-        <f>=(B459*1000000000)-(C459*10000000)+(D459*100000)+(B464*1000)-(C464*100)+(D464*10)+(E464*1)-(F464*0.01)</f>
+        <f>(B459*1000000000)-(C459*10000000)+(D459*100000)+(B464*1000)-(C464*100)+(D464*10)+(E464*1)-(F464*0.01)</f>
       </c>
       <c r="AC459" t="str">
-        <f>=(J459*1000000000)-(K459*10000000)+(L459*100000)+(J464*1000)-(K464*100)+(L464*10)+(M464*1)-(N464*0.01)</f>
+        <f>(J459*1000000000)-(K459*10000000)+(L459*100000)+(J464*1000)-(K464*100)+(L464*10)+(M464*1)-(N464*0.01)</f>
       </c>
     </row>
     <row r="460">
@@ -16618,10 +16618,10 @@
         <f>RANK(AC460,$AC$459:$AC$461)+COUNTIF($AC$458:AC459,AC460)</f>
       </c>
       <c r="U460" t="str">
-        <f>=(B460*1000000000)-(C460*10000000)+(D460*100000)+(B465*1000)-(C465*100)+(D465*10)+(E465*1)-(F465*0.01)</f>
+        <f>(B460*1000000000)-(C460*10000000)+(D460*100000)+(B465*1000)-(C465*100)+(D465*10)+(E465*1)-(F465*0.01)</f>
       </c>
       <c r="AC460" t="str">
-        <f>=(J460*1000000000)-(K460*10000000)+(L460*100000)+(J465*1000)-(K465*100)+(L465*10)+(M465*1)-(N465*0.01)</f>
+        <f>(J460*1000000000)-(K460*10000000)+(L460*100000)+(J465*1000)-(K465*100)+(L465*10)+(M465*1)-(N465*0.01)</f>
       </c>
     </row>
     <row r="461">
@@ -16656,10 +16656,10 @@
         <f>RANK(AC461,$AC$459:$AC$461)+COUNTIF($AC$458:AC460,AC461)</f>
       </c>
       <c r="U461" t="str">
-        <f>=(B461*1000000000)-(C461*10000000)+(D461*100000)+(B466*1000)-(C466*100)+(D466*10)+(E466*1)-(F466*0.01)</f>
+        <f>(B461*1000000000)-(C461*10000000)+(D461*100000)+(B466*1000)-(C466*100)+(D466*10)+(E466*1)-(F466*0.01)</f>
       </c>
       <c r="AC461" t="str">
-        <f>=(J461*1000000000)-(K461*10000000)+(L461*100000)+(J466*1000)-(K466*100)+(L466*10)+(M466*1)-(N466*0.01)</f>
+        <f>(J461*1000000000)-(K461*10000000)+(L461*100000)+(J466*1000)-(K466*100)+(L466*10)+(M466*1)-(N466*0.01)</f>
       </c>
     </row>
     <row r="463">
@@ -17514,10 +17514,10 @@
         <f>RANK(AC502,$AC$502:$AC$504)+COUNTIF($AC$501:AC501,AC502)</f>
       </c>
       <c r="U502" t="str">
-        <f>=(B502*1000000000)-(C502*10000000)+(D502*100000)+(B507*1000)-(C507*100)+(D507*10)+(E507*1)-(F507*0.01)</f>
+        <f>(B502*1000000000)-(C502*10000000)+(D502*100000)+(B507*1000)-(C507*100)+(D507*10)+(E507*1)-(F507*0.01)</f>
       </c>
       <c r="AC502" t="str">
-        <f>=(J502*1000000000)-(K502*10000000)+(L502*100000)+(J507*1000)-(K507*100)+(L507*10)+(M507*1)-(N507*0.01)</f>
+        <f>(J502*1000000000)-(K502*10000000)+(L502*100000)+(J507*1000)-(K507*100)+(L507*10)+(M507*1)-(N507*0.01)</f>
       </c>
     </row>
     <row r="503">
@@ -17552,10 +17552,10 @@
         <f>RANK(AC503,$AC$502:$AC$504)+COUNTIF($AC$501:AC502,AC503)</f>
       </c>
       <c r="U503" t="str">
-        <f>=(B503*1000000000)-(C503*10000000)+(D503*100000)+(B508*1000)-(C508*100)+(D508*10)+(E508*1)-(F508*0.01)</f>
+        <f>(B503*1000000000)-(C503*10000000)+(D503*100000)+(B508*1000)-(C508*100)+(D508*10)+(E508*1)-(F508*0.01)</f>
       </c>
       <c r="AC503" t="str">
-        <f>=(J503*1000000000)-(K503*10000000)+(L503*100000)+(J508*1000)-(K508*100)+(L508*10)+(M508*1)-(N508*0.01)</f>
+        <f>(J503*1000000000)-(K503*10000000)+(L503*100000)+(J508*1000)-(K508*100)+(L508*10)+(M508*1)-(N508*0.01)</f>
       </c>
     </row>
     <row r="504">
@@ -17590,10 +17590,10 @@
         <f>RANK(AC504,$AC$502:$AC$504)+COUNTIF($AC$501:AC503,AC504)</f>
       </c>
       <c r="U504" t="str">
-        <f>=(B504*1000000000)-(C504*10000000)+(D504*100000)+(B509*1000)-(C509*100)+(D509*10)+(E509*1)-(F509*0.01)</f>
+        <f>(B504*1000000000)-(C504*10000000)+(D504*100000)+(B509*1000)-(C509*100)+(D509*10)+(E509*1)-(F509*0.01)</f>
       </c>
       <c r="AC504" t="str">
-        <f>=(J504*1000000000)-(K504*10000000)+(L504*100000)+(J509*1000)-(K509*100)+(L509*10)+(M509*1)-(N509*0.01)</f>
+        <f>(J504*1000000000)-(K504*10000000)+(L504*100000)+(J509*1000)-(K509*100)+(L509*10)+(M509*1)-(N509*0.01)</f>
       </c>
     </row>
     <row r="506">
@@ -18448,10 +18448,10 @@
         <f>RANK(AC545,$AC$545:$AC$547)+COUNTIF($AC$544:AC544,AC545)</f>
       </c>
       <c r="U545" t="str">
-        <f>=(B545*1000000000)-(C545*10000000)+(D545*100000)+(B550*1000)-(C550*100)+(D550*10)+(E550*1)-(F550*0.01)</f>
+        <f>(B545*1000000000)-(C545*10000000)+(D545*100000)+(B550*1000)-(C550*100)+(D550*10)+(E550*1)-(F550*0.01)</f>
       </c>
       <c r="AC545" t="str">
-        <f>=(J545*1000000000)-(K545*10000000)+(L545*100000)+(J550*1000)-(K550*100)+(L550*10)+(M550*1)-(N550*0.01)</f>
+        <f>(J545*1000000000)-(K545*10000000)+(L545*100000)+(J550*1000)-(K550*100)+(L550*10)+(M550*1)-(N550*0.01)</f>
       </c>
     </row>
     <row r="546">
@@ -18486,10 +18486,10 @@
         <f>RANK(AC546,$AC$545:$AC$547)+COUNTIF($AC$544:AC545,AC546)</f>
       </c>
       <c r="U546" t="str">
-        <f>=(B546*1000000000)-(C546*10000000)+(D546*100000)+(B551*1000)-(C551*100)+(D551*10)+(E551*1)-(F551*0.01)</f>
+        <f>(B546*1000000000)-(C546*10000000)+(D546*100000)+(B551*1000)-(C551*100)+(D551*10)+(E551*1)-(F551*0.01)</f>
       </c>
       <c r="AC546" t="str">
-        <f>=(J546*1000000000)-(K546*10000000)+(L546*100000)+(J551*1000)-(K551*100)+(L551*10)+(M551*1)-(N551*0.01)</f>
+        <f>(J546*1000000000)-(K546*10000000)+(L546*100000)+(J551*1000)-(K551*100)+(L551*10)+(M551*1)-(N551*0.01)</f>
       </c>
     </row>
     <row r="547">
@@ -18524,10 +18524,10 @@
         <f>RANK(AC547,$AC$545:$AC$547)+COUNTIF($AC$544:AC546,AC547)</f>
       </c>
       <c r="U547" t="str">
-        <f>=(B547*1000000000)-(C547*10000000)+(D547*100000)+(B552*1000)-(C552*100)+(D552*10)+(E552*1)-(F552*0.01)</f>
+        <f>(B547*1000000000)-(C547*10000000)+(D547*100000)+(B552*1000)-(C552*100)+(D552*10)+(E552*1)-(F552*0.01)</f>
       </c>
       <c r="AC547" t="str">
-        <f>=(J547*1000000000)-(K547*10000000)+(L547*100000)+(J552*1000)-(K552*100)+(L552*10)+(M552*1)-(N552*0.01)</f>
+        <f>(J547*1000000000)-(K547*10000000)+(L547*100000)+(J552*1000)-(K552*100)+(L552*10)+(M552*1)-(N552*0.01)</f>
       </c>
     </row>
     <row r="549">
@@ -19382,10 +19382,10 @@
         <f>RANK(AC588,$AC$588:$AC$590)+COUNTIF($AC$587:AC587,AC588)</f>
       </c>
       <c r="U588" t="str">
-        <f>=(B588*1000000000)-(C588*10000000)+(D588*100000)+(B593*1000)-(C593*100)+(D593*10)+(E593*1)-(F593*0.01)</f>
+        <f>(B588*1000000000)-(C588*10000000)+(D588*100000)+(B593*1000)-(C593*100)+(D593*10)+(E593*1)-(F593*0.01)</f>
       </c>
       <c r="AC588" t="str">
-        <f>=(J588*1000000000)-(K588*10000000)+(L588*100000)+(J593*1000)-(K593*100)+(L593*10)+(M593*1)-(N593*0.01)</f>
+        <f>(J588*1000000000)-(K588*10000000)+(L588*100000)+(J593*1000)-(K593*100)+(L593*10)+(M593*1)-(N593*0.01)</f>
       </c>
     </row>
     <row r="589">
@@ -19420,10 +19420,10 @@
         <f>RANK(AC589,$AC$588:$AC$590)+COUNTIF($AC$587:AC588,AC589)</f>
       </c>
       <c r="U589" t="str">
-        <f>=(B589*1000000000)-(C589*10000000)+(D589*100000)+(B594*1000)-(C594*100)+(D594*10)+(E594*1)-(F594*0.01)</f>
+        <f>(B589*1000000000)-(C589*10000000)+(D589*100000)+(B594*1000)-(C594*100)+(D594*10)+(E594*1)-(F594*0.01)</f>
       </c>
       <c r="AC589" t="str">
-        <f>=(J589*1000000000)-(K589*10000000)+(L589*100000)+(J594*1000)-(K594*100)+(L594*10)+(M594*1)-(N594*0.01)</f>
+        <f>(J589*1000000000)-(K589*10000000)+(L589*100000)+(J594*1000)-(K594*100)+(L594*10)+(M594*1)-(N594*0.01)</f>
       </c>
     </row>
     <row r="590">
@@ -19458,10 +19458,10 @@
         <f>RANK(AC590,$AC$588:$AC$590)+COUNTIF($AC$587:AC589,AC590)</f>
       </c>
       <c r="U590" t="str">
-        <f>=(B590*1000000000)-(C590*10000000)+(D590*100000)+(B595*1000)-(C595*100)+(D595*10)+(E595*1)-(F595*0.01)</f>
+        <f>(B590*1000000000)-(C590*10000000)+(D590*100000)+(B595*1000)-(C595*100)+(D595*10)+(E595*1)-(F595*0.01)</f>
       </c>
       <c r="AC590" t="str">
-        <f>=(J590*1000000000)-(K590*10000000)+(L590*100000)+(J595*1000)-(K595*100)+(L595*10)+(M595*1)-(N595*0.01)</f>
+        <f>(J590*1000000000)-(K590*10000000)+(L590*100000)+(J595*1000)-(K595*100)+(L595*10)+(M595*1)-(N595*0.01)</f>
       </c>
     </row>
     <row r="592">
@@ -20142,10 +20142,10 @@
         <f>RANK(AC631,$AC$631:$AC$632)+COUNTIF($AC$630:AC630,AC631)</f>
       </c>
       <c r="U631" t="str">
-        <f>=(B631*1000000000)-(C631*10000000)+(D631*100000)+(B636*1000)-(C636*100)+(D636*10)+(E636*1)-(F636*0.01)</f>
+        <f>(B631*1000000000)-(C631*10000000)+(D631*100000)+(B636*1000)-(C636*100)+(D636*10)+(E636*1)-(F636*0.01)</f>
       </c>
       <c r="AC631" t="str">
-        <f>=(J631*1000000000)-(K631*10000000)+(L631*100000)+(J635*1000)-(K635*100)+(L635*10)+(M635*1)-(N635*0.01)</f>
+        <f>(J631*1000000000)-(K631*10000000)+(L631*100000)+(J635*1000)-(K635*100)+(L635*10)+(M635*1)-(N635*0.01)</f>
       </c>
     </row>
     <row r="632">
@@ -20180,10 +20180,10 @@
         <f>RANK(AC632,$AC$631:$AC$632)+COUNTIF($AC$630:AC631,AC632)</f>
       </c>
       <c r="U632" t="str">
-        <f>=(B632*1000000000)-(C632*10000000)+(D632*100000)+(B637*1000)-(C637*100)+(D637*10)+(E637*1)-(F637*0.01)</f>
+        <f>(B632*1000000000)-(C632*10000000)+(D632*100000)+(B637*1000)-(C637*100)+(D637*10)+(E637*1)-(F637*0.01)</f>
       </c>
       <c r="AC632" t="str">
-        <f>=(J632*1000000000)-(K632*10000000)+(L632*100000)+(J636*1000)-(K636*100)+(L636*10)+(M636*1)-(N636*0.01)</f>
+        <f>(J632*1000000000)-(K632*10000000)+(L632*100000)+(J636*1000)-(K636*100)+(L636*10)+(M636*1)-(N636*0.01)</f>
       </c>
     </row>
     <row r="633">
@@ -20203,7 +20203,7 @@
         <f>RANK(U633,$U$631:$U$633)+COUNTIF($U$630:U632,U633)</f>
       </c>
       <c r="U633" t="str">
-        <f>=(B633*1000000000)-(C633*10000000)+(D633*100000)+(B638*1000)-(C638*100)+(D638*10)+(E638*1)-(F638*0.01)</f>
+        <f>(B633*1000000000)-(C633*10000000)+(D633*100000)+(B638*1000)-(C638*100)+(D638*10)+(E638*1)-(F638*0.01)</f>
       </c>
     </row>
     <row r="634">
@@ -20536,7 +20536,7 @@
         <f>RANK(U658,$U$658:$U$659)+COUNTIF($U$657:U657,U658)</f>
       </c>
       <c r="U658" t="str">
-        <f>=(B658*1000000000)-(C658*10000000)+(D658*100000)+(B662*1000)-(C662*100)+(D662*10)+(E662*1)-(F662*0.01)</f>
+        <f>(B658*1000000000)-(C658*10000000)+(D658*100000)+(B662*1000)-(C662*100)+(D662*10)+(E662*1)-(F662*0.01)</f>
       </c>
     </row>
     <row r="659">
@@ -20556,7 +20556,7 @@
         <f>RANK(U659,$U$658:$U$659)+COUNTIF($U$657:U658,U659)</f>
       </c>
       <c r="U659" t="str">
-        <f>=(B659*1000000000)-(C659*10000000)+(D659*100000)+(B663*1000)-(C663*100)+(D663*10)+(E663*1)-(F663*0.01)</f>
+        <f>(B659*1000000000)-(C659*10000000)+(D659*100000)+(B663*1000)-(C663*100)+(D663*10)+(E663*1)-(F663*0.01)</f>
       </c>
     </row>
     <row r="661">

--- a/pools-example-large-teams-max-size.xlsx
+++ b/pools-example-large-teams-max-size.xlsx
@@ -6641,17 +6641,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -6660,17 +6660,17 @@
         <f>'data'!$B$51</f>
       </c>
       <c r="J4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N4" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
         <f>'data'!$B$50</f>
@@ -6829,17 +6829,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D13:D17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13:E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13:F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13:B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13:C17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -6848,17 +6848,17 @@
         <f>'data'!$B$52</f>
       </c>
       <c r="J12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L13:L17)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13:M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13:N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13:J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13:K17," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
         <f>'data'!$B$50</f>
@@ -7017,17 +7017,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
         <f>'data'!$B$4</f>
@@ -7036,17 +7036,17 @@
         <f>'data'!$B$52</f>
       </c>
       <c r="J20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N20" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
         <f>'data'!$B$51</f>
@@ -7575,17 +7575,17 @@
         <f>'data'!$B$7</f>
       </c>
       <c r="B47" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D48:D52)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48:B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48:C52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48:E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48:F52," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C47" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48:B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48:C52," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48:E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48:F52," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F47" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D48:D52)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48:E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48:F52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48:B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48:C52," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G47" s="14" t="str">
         <f>'data'!$B$6</f>
@@ -7594,17 +7594,17 @@
         <f>'data'!$B$54</f>
       </c>
       <c r="J47" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L48:L52)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48:J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48:K52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48:M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48:N52," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K47" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48:J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48:K52," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L47" s="18"/>
       <c r="M47" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48:M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48:N52," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N47" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L48:L52)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48:M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48:N52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48:J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48:K52," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O47" s="14" t="str">
         <f>'data'!$B$53</f>
@@ -7763,17 +7763,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B55" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D56:D60)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56:B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56:C60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56:E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56:F60," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C55" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56:B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56:C60," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56:E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56:F60," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F55" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D56:D60)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56:E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56:F60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56:B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56:C60," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G55" s="14" t="str">
         <f>'data'!$B$6</f>
@@ -7782,17 +7782,17 @@
         <f>'data'!$B$55</f>
       </c>
       <c r="J55" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L56:L60)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56:J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56:K60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56:M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56:N60," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K55" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56:J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56:K60," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56:M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56:N60," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N55" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L56:L60)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56:M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56:N60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56:J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56:K60," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O55" s="14" t="str">
         <f>'data'!$B$53</f>
@@ -7951,17 +7951,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B63" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D64:D68)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64:B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64:C68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64:E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64:F68," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C63" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64:B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64:C68," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64:E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64:F68," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F63" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D64:D68)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64:E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64:F68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64:B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64:C68," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G63" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -7970,17 +7970,17 @@
         <f>'data'!$B$55</f>
       </c>
       <c r="J63" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L64:L68)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64:J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64:K68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64:M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64:N68," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K63" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64:J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64:K68," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64:M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64:N68," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N63" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L64:L68)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64:M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64:N68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64:J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64:K68," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O63" s="14" t="str">
         <f>'data'!$B$54</f>
@@ -8509,17 +8509,17 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="B90" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D91:D95)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91:B95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91:C95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91:E95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91:F95," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C90" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91:B95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91:C95," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91:E95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91:F95," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F90" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D91:D95)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91:E95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91:F95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91:B95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91:C95," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G90" s="14" t="str">
         <f>'data'!$B$9</f>
@@ -8528,17 +8528,17 @@
         <f>'data'!$B$57</f>
       </c>
       <c r="J90" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L91:L95)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91:J95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91:K95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91:M95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91:N95," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K90" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91:J95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91:K95," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L90" s="18"/>
       <c r="M90" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91:M95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91:N95," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N90" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L91:L95)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91:M95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91:N95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91:J95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91:K95," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O90" s="14" t="str">
         <f>'data'!$B$56</f>
@@ -8697,17 +8697,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B98" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D99:D103)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99:B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99:C103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99:E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99:F103," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C98" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99:B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99:C103," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D98" s="18"/>
       <c r="E98" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99:E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99:F103," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F98" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D99:D103)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99:E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99:F103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99:B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99:C103," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G98" s="14" t="str">
         <f>'data'!$B$9</f>
@@ -8716,17 +8716,17 @@
         <f>'data'!$B$58</f>
       </c>
       <c r="J98" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L99:L103)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99:J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99:K103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99:M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99:N103," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K98" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99:J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99:K103," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L98" s="18"/>
       <c r="M98" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99:M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99:N103," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N98" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L99:L103)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99:M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99:N103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99:J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99:K103," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O98" s="14" t="str">
         <f>'data'!$B$56</f>
@@ -8885,17 +8885,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B106" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D107:D111)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107:B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107:C111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107:E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107:F111," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C106" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107:B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107:C111," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D106" s="18"/>
       <c r="E106" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107:E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107:F111," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F106" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D107:D111)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107:E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107:F111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107:B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107:C111," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G106" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -8904,17 +8904,17 @@
         <f>'data'!$B$58</f>
       </c>
       <c r="J106" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L107:L111)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107:J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107:K111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107:M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107:N111," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K106" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107:J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107:K111," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L106" s="18"/>
       <c r="M106" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107:M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107:N111," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N106" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L107:L111)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107:M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107:N111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107:J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107:K111," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O106" s="14" t="str">
         <f>'data'!$B$57</f>
@@ -9443,17 +9443,17 @@
         <f>'data'!$B$13</f>
       </c>
       <c r="B133" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D134:D138)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134:B138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134:C138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134:E138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134:F138," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C133" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134:B138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134:C138," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D133" s="18"/>
       <c r="E133" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134:E138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134:F138," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F133" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D134:D138)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134:E138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134:F138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134:B138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134:C138," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G133" s="14" t="str">
         <f>'data'!$B$12</f>
@@ -9462,17 +9462,17 @@
         <f>'data'!$B$60</f>
       </c>
       <c r="J133" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L134:L138)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134:J138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134:K138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134:M138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134:N138," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K133" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134:J138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134:K138," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L133" s="18"/>
       <c r="M133" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134:M138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134:N138," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N133" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L134:L138)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134:M138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134:N138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134:J138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134:K138," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O133" s="14" t="str">
         <f>'data'!$B$59</f>
@@ -9631,17 +9631,17 @@
         <f>'data'!$B$14</f>
       </c>
       <c r="B141" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D142:D146)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142:B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142:C146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142:E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142:F146," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C141" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142:B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142:C146," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D141" s="18"/>
       <c r="E141" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142:E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142:F146," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F141" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D142:D146)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142:E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142:F146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142:B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142:C146," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G141" s="14" t="str">
         <f>'data'!$B$12</f>
@@ -9650,17 +9650,17 @@
         <f>'data'!$B$61</f>
       </c>
       <c r="J141" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L142:L146)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142:J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142:K146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142:M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142:N146," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K141" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142:J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142:K146," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L141" s="18"/>
       <c r="M141" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142:M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142:N146," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N141" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L142:L146)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142:M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142:N146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142:J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142:K146," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O141" s="14" t="str">
         <f>'data'!$B$59</f>
@@ -9819,17 +9819,17 @@
         <f>'data'!$B$14</f>
       </c>
       <c r="B149" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D150:D154)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150:B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150:C154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150:E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150:F154," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C149" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150:B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150:C154," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D149" s="18"/>
       <c r="E149" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150:E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150:F154," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F149" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D150:D154)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150:E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150:F154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150:B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150:C154," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G149" s="14" t="str">
         <f>'data'!$B$13</f>
@@ -9838,17 +9838,17 @@
         <f>'data'!$B$61</f>
       </c>
       <c r="J149" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L150:L154)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150:J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150:K154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150:M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150:N154," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K149" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150:J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150:K154," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L149" s="18"/>
       <c r="M149" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150:M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150:N154," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N149" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L150:L154)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150:M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150:N154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150:J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150:K154," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O149" s="14" t="str">
         <f>'data'!$B$60</f>
@@ -10377,17 +10377,17 @@
         <f>'data'!$B$16</f>
       </c>
       <c r="B176" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D177:D181)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177:B181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177:C181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177:E181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177:F181," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C176" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177:B181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177:C181," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D176" s="18"/>
       <c r="E176" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177:E181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177:F181," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F176" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D177:D181)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177:E181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177:F181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177:B181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177:C181," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G176" s="14" t="str">
         <f>'data'!$B$15</f>
@@ -10396,17 +10396,17 @@
         <f>'data'!$B$63</f>
       </c>
       <c r="J176" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L177:L181)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177:J181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177:K181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177:M181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177:N181," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K176" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177:J181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177:K181," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L176" s="18"/>
       <c r="M176" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177:M181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177:N181," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N176" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L177:L181)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177:M181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177:N181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177:J181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177:K181," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O176" s="14" t="str">
         <f>'data'!$B$62</f>
@@ -10565,17 +10565,17 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="B184" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D185:D189)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185:B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185:C189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185:E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185:F189," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C184" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185:B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185:C189," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D184" s="18"/>
       <c r="E184" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185:E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185:F189," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F184" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D185:D189)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185:E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185:F189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185:B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185:C189," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G184" s="14" t="str">
         <f>'data'!$B$15</f>
@@ -10584,17 +10584,17 @@
         <f>'data'!$B$64</f>
       </c>
       <c r="J184" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L185:L189)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185:J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185:K189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185:M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185:N189," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K184" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185:J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185:K189," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L184" s="18"/>
       <c r="M184" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185:M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185:N189," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N184" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L185:L189)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185:M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185:N189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185:J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185:K189," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O184" s="14" t="str">
         <f>'data'!$B$62</f>
@@ -10753,17 +10753,17 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="B192" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D193:D197)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193:B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193:C197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193:E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193:F197," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C192" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193:B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193:C197," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D192" s="18"/>
       <c r="E192" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193:E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193:F197," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F192" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D193:D197)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193:E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193:F197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193:B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193:C197," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G192" s="14" t="str">
         <f>'data'!$B$16</f>
@@ -10772,17 +10772,17 @@
         <f>'data'!$B$64</f>
       </c>
       <c r="J192" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L193:L197)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193:J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193:K197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193:M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193:N197," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K192" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193:J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193:K197," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L192" s="18"/>
       <c r="M192" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193:M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193:N197," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N192" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L193:L197)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193:M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193:N197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193:J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193:K197," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O192" s="14" t="str">
         <f>'data'!$B$63</f>
@@ -11311,17 +11311,17 @@
         <f>'data'!$B$19</f>
       </c>
       <c r="B219" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D220:D224)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220:B224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220:C224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220:E224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220:F224," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C219" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220:B224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220:C224," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D219" s="18"/>
       <c r="E219" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220:E224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220:F224," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F219" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D220:D224)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220:E224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220:F224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220:B224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220:C224," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G219" s="14" t="str">
         <f>'data'!$B$18</f>
@@ -11330,17 +11330,17 @@
         <f>'data'!$B$66</f>
       </c>
       <c r="J219" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L220:L224)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220:J224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220:K224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220:M224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220:N224," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K219" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220:J224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220:K224," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L219" s="18"/>
       <c r="M219" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220:M224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220:N224," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N219" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L220:L224)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220:M224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220:N224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220:J224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220:K224," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O219" s="14" t="str">
         <f>'data'!$B$65</f>
@@ -11499,17 +11499,17 @@
         <f>'data'!$B$20</f>
       </c>
       <c r="B227" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D228:D232)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228:B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228:C232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228:E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228:F232," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C227" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228:B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228:C232," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D227" s="18"/>
       <c r="E227" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228:E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228:F232," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F227" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D228:D232)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228:E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228:F232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228:B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228:C232," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G227" s="14" t="str">
         <f>'data'!$B$18</f>
@@ -11518,17 +11518,17 @@
         <f>'data'!$B$67</f>
       </c>
       <c r="J227" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L228:L232)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228:J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228:K232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228:M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228:N232," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K227" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228:J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228:K232," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L227" s="18"/>
       <c r="M227" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228:M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228:N232," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N227" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L228:L232)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228:M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228:N232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228:J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228:K232," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O227" s="14" t="str">
         <f>'data'!$B$65</f>
@@ -11687,17 +11687,17 @@
         <f>'data'!$B$20</f>
       </c>
       <c r="B235" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D236:D240)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236:B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236:C240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236:E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236:F240," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C235" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236:B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236:C240," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D235" s="18"/>
       <c r="E235" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236:E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236:F240," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F235" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D236:D240)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236:E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236:F240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236:B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236:C240," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G235" s="14" t="str">
         <f>'data'!$B$19</f>
@@ -11706,17 +11706,17 @@
         <f>'data'!$B$67</f>
       </c>
       <c r="J235" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L236:L240)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236:J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236:K240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236:M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236:N240," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K235" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236:J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236:K240," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L235" s="18"/>
       <c r="M235" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236:M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236:N240," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N235" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L236:L240)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236:M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236:N240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236:J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236:K240," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O235" s="14" t="str">
         <f>'data'!$B$66</f>
@@ -12245,17 +12245,17 @@
         <f>'data'!$B$22</f>
       </c>
       <c r="B262" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D263:D267)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263:B267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263:C267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263:E267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263:F267," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C262" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263:B267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263:C267," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D262" s="18"/>
       <c r="E262" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263:E267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263:F267," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F262" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D263:D267)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263:E267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263:F267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263:B267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263:C267," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G262" s="14" t="str">
         <f>'data'!$B$21</f>
@@ -12264,17 +12264,17 @@
         <f>'data'!$B$69</f>
       </c>
       <c r="J262" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L263:L267)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263:J267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263:K267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263:M267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263:N267," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K262" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263:J267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263:K267," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L262" s="18"/>
       <c r="M262" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263:M267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263:N267," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N262" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L263:L267)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263:M267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263:N267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263:J267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263:K267," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O262" s="14" t="str">
         <f>'data'!$B$68</f>
@@ -12433,17 +12433,17 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="B270" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D271:D275)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271:B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271:C275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271:E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271:F275," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C270" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271:B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271:C275," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D270" s="18"/>
       <c r="E270" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271:E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271:F275," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F270" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D271:D275)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271:E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271:F275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271:B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271:C275," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G270" s="14" t="str">
         <f>'data'!$B$21</f>
@@ -12452,17 +12452,17 @@
         <f>'data'!$B$70</f>
       </c>
       <c r="J270" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L271:L275)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271:J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271:K275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271:M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271:N275," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K270" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271:J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271:K275," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L270" s="18"/>
       <c r="M270" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271:M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271:N275," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N270" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L271:L275)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271:M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271:N275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271:J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271:K275," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O270" s="14" t="str">
         <f>'data'!$B$68</f>
@@ -12621,17 +12621,17 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="B278" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D279:D283)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279:B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279:C283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279:E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279:F283," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C278" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279:B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279:C283," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D278" s="18"/>
       <c r="E278" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279:E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279:F283," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F278" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D279:D283)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279:E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279:F283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279:B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279:C283," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G278" s="14" t="str">
         <f>'data'!$B$22</f>
@@ -12640,17 +12640,17 @@
         <f>'data'!$B$70</f>
       </c>
       <c r="J278" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L279:L283)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279:J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279:K283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279:M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279:N283," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K278" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279:J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279:K283," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L278" s="18"/>
       <c r="M278" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279:M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279:N283," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N278" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L279:L283)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279:M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279:N283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279:J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279:K283," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O278" s="14" t="str">
         <f>'data'!$B$69</f>
@@ -13179,17 +13179,17 @@
         <f>'data'!$B$25</f>
       </c>
       <c r="B305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D306:D310)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306:B310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306:C310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306:E310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306:F310," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306:B310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306:C310," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D305" s="18"/>
       <c r="E305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306:E310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306:F310," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D306:D310)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306:E310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306:F310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306:B310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306:C310," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G305" s="14" t="str">
         <f>'data'!$B$24</f>
@@ -13198,17 +13198,17 @@
         <f>'data'!$B$72</f>
       </c>
       <c r="J305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L306:L310)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306:J310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306:K310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306:M310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306:N310," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306:J310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306:K310," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L305" s="18"/>
       <c r="M305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306:M310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306:N310," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L306:L310)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306:M310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306:N310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306:J310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306:K310," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O305" s="14" t="str">
         <f>'data'!$B$71</f>
@@ -13367,17 +13367,17 @@
         <f>'data'!$B$26</f>
       </c>
       <c r="B313" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D314:D318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C313" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D313" s="18"/>
       <c r="E313" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F313" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D314:D318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G313" s="14" t="str">
         <f>'data'!$B$24</f>
@@ -13386,17 +13386,17 @@
         <f>'data'!$B$73</f>
       </c>
       <c r="J313" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L314:L318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K313" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L313" s="18"/>
       <c r="M313" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N313" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L314:L318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O313" s="14" t="str">
         <f>'data'!$B$71</f>
@@ -13555,17 +13555,17 @@
         <f>'data'!$B$26</f>
       </c>
       <c r="B321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D322:D326)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322:B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322:C326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322:E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322:F326," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322:B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322:C326," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D321" s="18"/>
       <c r="E321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322:E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322:F326," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D322:D326)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322:E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322:F326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322:B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322:C326," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G321" s="14" t="str">
         <f>'data'!$B$25</f>
@@ -13574,17 +13574,17 @@
         <f>'data'!$B$73</f>
       </c>
       <c r="J321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L322:L326)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322:J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322:K326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322:M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322:N326," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322:J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322:K326," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L321" s="18"/>
       <c r="M321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322:M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322:N326," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L322:L326)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322:M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322:N326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322:J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322:K326," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O321" s="14" t="str">
         <f>'data'!$B$72</f>
@@ -14113,17 +14113,17 @@
         <f>'data'!$B$28</f>
       </c>
       <c r="B348" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D349:D353)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349:B353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349:C353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349:E353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349:F353," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C348" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349:B353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349:C353," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D348" s="18"/>
       <c r="E348" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349:E353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349:F353," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F348" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D349:D353)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349:E353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349:F353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349:B353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349:C353," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G348" s="14" t="str">
         <f>'data'!$B$27</f>
@@ -14132,17 +14132,17 @@
         <f>'data'!$B$75</f>
       </c>
       <c r="J348" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L349:L353)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349:J353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349:K353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349:M353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349:N353," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K348" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349:J353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349:K353," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L348" s="18"/>
       <c r="M348" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349:M353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349:N353," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N348" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L349:L353)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349:M353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349:N353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349:J353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349:K353," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O348" s="14" t="str">
         <f>'data'!$B$74</f>
@@ -14301,17 +14301,17 @@
         <f>'data'!$B$29</f>
       </c>
       <c r="B356" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D357:D361)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357:B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357:C361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357:E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357:F361," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C356" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357:B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357:C361," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D356" s="18"/>
       <c r="E356" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357:E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357:F361," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F356" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D357:D361)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357:E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357:F361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357:B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357:C361," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G356" s="14" t="str">
         <f>'data'!$B$27</f>
@@ -14320,17 +14320,17 @@
         <f>'data'!$B$76</f>
       </c>
       <c r="J356" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L357:L361)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357:J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357:K361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357:M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357:N361," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K356" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357:J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357:K361," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L356" s="18"/>
       <c r="M356" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357:M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357:N361," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N356" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L357:L361)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357:M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357:N361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357:J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357:K361," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O356" s="14" t="str">
         <f>'data'!$B$74</f>
@@ -14489,17 +14489,17 @@
         <f>'data'!$B$29</f>
       </c>
       <c r="B364" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D365:D369)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365:B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365:C369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365:E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365:F369," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C364" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365:B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365:C369," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D364" s="18"/>
       <c r="E364" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365:E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365:F369," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F364" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D365:D369)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365:E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365:F369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365:B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365:C369," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G364" s="14" t="str">
         <f>'data'!$B$28</f>
@@ -14508,17 +14508,17 @@
         <f>'data'!$B$76</f>
       </c>
       <c r="J364" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L365:L369)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365:J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365:K369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365:M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365:N369," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K364" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365:J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365:K369," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L364" s="18"/>
       <c r="M364" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365:M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365:N369," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N364" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L365:L369)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365:M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365:N369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365:J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365:K369," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O364" s="14" t="str">
         <f>'data'!$B$75</f>
@@ -15047,17 +15047,17 @@
         <f>'data'!$B$31</f>
       </c>
       <c r="B391" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D392:D396)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392:B396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392:C396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392:E396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392:F396," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C391" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392:B396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392:C396," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D391" s="18"/>
       <c r="E391" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392:E396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392:F396," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F391" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D392:D396)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392:E396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392:F396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392:B396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392:C396," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G391" s="14" t="str">
         <f>'data'!$B$30</f>
@@ -15066,17 +15066,17 @@
         <f>'data'!$B$78</f>
       </c>
       <c r="J391" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L392:L396)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392:J396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392:K396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392:M396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392:N396," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K391" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392:J396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392:K396," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L391" s="18"/>
       <c r="M391" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392:M396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392:N396," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N391" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L392:L396)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392:M396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392:N396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392:J396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392:K396," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O391" s="14" t="str">
         <f>'data'!$B$77</f>
@@ -15235,17 +15235,17 @@
         <f>'data'!$B$32</f>
       </c>
       <c r="B399" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D400:D404)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400:B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400:C404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400:E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400:F404," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C399" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400:B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400:C404," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D399" s="18"/>
       <c r="E399" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400:E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400:F404," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F399" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D400:D404)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400:E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400:F404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400:B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400:C404," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G399" s="14" t="str">
         <f>'data'!$B$30</f>
@@ -15254,17 +15254,17 @@
         <f>'data'!$B$79</f>
       </c>
       <c r="J399" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L400:L404)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400:J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400:K404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400:M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400:N404," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K399" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400:J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400:K404," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L399" s="18"/>
       <c r="M399" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400:M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400:N404," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N399" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L400:L404)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400:M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400:N404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400:J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400:K404," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O399" s="14" t="str">
         <f>'data'!$B$77</f>
@@ -15423,17 +15423,17 @@
         <f>'data'!$B$32</f>
       </c>
       <c r="B407" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D408:D412)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408:B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408:C412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408:E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408:F412," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C407" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408:B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408:C412," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D407" s="18"/>
       <c r="E407" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408:E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408:F412," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F407" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D408:D412)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408:E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408:F412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408:B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408:C412," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G407" s="14" t="str">
         <f>'data'!$B$31</f>
@@ -15442,17 +15442,17 @@
         <f>'data'!$B$79</f>
       </c>
       <c r="J407" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L408:L412)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408:J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408:K412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408:M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408:N412," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K407" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408:J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408:K412," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L407" s="18"/>
       <c r="M407" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408:M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408:N412," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N407" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L408:L412)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408:M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408:N412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408:J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408:K412," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O407" s="14" t="str">
         <f>'data'!$B$78</f>
@@ -15981,17 +15981,17 @@
         <f>'data'!$B$34</f>
       </c>
       <c r="B434" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D435:D439)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435:B439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435:C439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435:E439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435:F439," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C434" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435:B439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435:C439," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D434" s="18"/>
       <c r="E434" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435:E439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435:F439," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F434" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D435:D439)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435:E439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435:F439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435:B439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435:C439," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G434" s="14" t="str">
         <f>'data'!$B$33</f>
@@ -16000,17 +16000,17 @@
         <f>'data'!$B$81</f>
       </c>
       <c r="J434" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L435:L439)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435:J439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435:K439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435:M439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435:N439," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K434" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435:J439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435:K439," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L434" s="18"/>
       <c r="M434" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435:M439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435:N439," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N434" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L435:L439)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435:M439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435:N439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435:J439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435:K439," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O434" s="14" t="str">
         <f>'data'!$B$80</f>
@@ -16169,17 +16169,17 @@
         <f>'data'!$B$35</f>
       </c>
       <c r="B442" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D443:D447)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443:B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443:C447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443:E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443:F447," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C442" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443:B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443:C447," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D442" s="18"/>
       <c r="E442" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443:E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443:F447," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F442" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D443:D447)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443:E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443:F447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443:B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443:C447," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G442" s="14" t="str">
         <f>'data'!$B$33</f>
@@ -16188,17 +16188,17 @@
         <f>'data'!$B$82</f>
       </c>
       <c r="J442" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L443:L447)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443:J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443:K447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443:M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443:N447," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K442" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443:J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443:K447," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L442" s="18"/>
       <c r="M442" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443:M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443:N447," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N442" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L443:L447)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443:M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443:N447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443:J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443:K447," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O442" s="14" t="str">
         <f>'data'!$B$80</f>
@@ -16357,17 +16357,17 @@
         <f>'data'!$B$35</f>
       </c>
       <c r="B450" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D451:D455)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451:B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451:C455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451:E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451:F455," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C450" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451:B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451:C455," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D450" s="18"/>
       <c r="E450" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451:E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451:F455," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F450" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D451:D455)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451:E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451:F455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451:B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451:C455," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G450" s="14" t="str">
         <f>'data'!$B$34</f>
@@ -16376,17 +16376,17 @@
         <f>'data'!$B$82</f>
       </c>
       <c r="J450" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L451:L455)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451:J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451:K455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451:M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451:N455," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K450" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451:J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451:K455," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L450" s="18"/>
       <c r="M450" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451:M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451:N455," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N450" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L451:L455)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451:M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451:N455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451:J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451:K455," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O450" s="14" t="str">
         <f>'data'!$B$81</f>
@@ -16915,17 +16915,17 @@
         <f>'data'!$B$37</f>
       </c>
       <c r="B477" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D478:D482)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478:B482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478:C482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478:E482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478:F482," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C477" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478:B482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478:C482," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D477" s="18"/>
       <c r="E477" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478:E482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478:F482," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F477" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D478:D482)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478:E482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478:F482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478:B482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478:C482," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G477" s="14" t="str">
         <f>'data'!$B$36</f>
@@ -16934,17 +16934,17 @@
         <f>'data'!$B$84</f>
       </c>
       <c r="J477" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L478:L482)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478:J482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478:K482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478:M482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478:N482," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K477" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478:J482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478:K482," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L477" s="18"/>
       <c r="M477" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478:M482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478:N482," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N477" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L478:L482)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478:M482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478:N482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478:J482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478:K482," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O477" s="14" t="str">
         <f>'data'!$B$83</f>
@@ -17103,17 +17103,17 @@
         <f>'data'!$B$38</f>
       </c>
       <c r="B485" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D486:D490)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486:B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486:C490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486:E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486:F490," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C485" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486:B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486:C490," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D485" s="18"/>
       <c r="E485" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486:E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486:F490," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F485" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D486:D490)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486:E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486:F490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486:B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486:C490," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G485" s="14" t="str">
         <f>'data'!$B$36</f>
@@ -17122,17 +17122,17 @@
         <f>'data'!$B$85</f>
       </c>
       <c r="J485" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L486:L490)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486:J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486:K490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486:M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486:N490," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K485" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486:J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486:K490," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L485" s="18"/>
       <c r="M485" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486:M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486:N490," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N485" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L486:L490)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486:M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486:N490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486:J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486:K490," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O485" s="14" t="str">
         <f>'data'!$B$83</f>
@@ -17291,17 +17291,17 @@
         <f>'data'!$B$38</f>
       </c>
       <c r="B493" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D494:D498)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494:B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494:C498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494:E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494:F498," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C493" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494:B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494:C498," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D493" s="18"/>
       <c r="E493" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494:E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494:F498," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F493" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D494:D498)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494:E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494:F498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494:B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494:C498," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G493" s="14" t="str">
         <f>'data'!$B$37</f>
@@ -17310,17 +17310,17 @@
         <f>'data'!$B$85</f>
       </c>
       <c r="J493" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L494:L498)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494:J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494:K498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494:M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494:N498," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K493" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494:J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494:K498," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L493" s="18"/>
       <c r="M493" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494:M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494:N498," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N493" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L494:L498)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494:M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494:N498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494:J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494:K498," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O493" s="14" t="str">
         <f>'data'!$B$84</f>
@@ -17849,17 +17849,17 @@
         <f>'data'!$B$40</f>
       </c>
       <c r="B520" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D521:D525)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521:B525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521:C525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521:E525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521:F525," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C520" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521:B525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521:C525," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D520" s="18"/>
       <c r="E520" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521:E525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521:F525," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F520" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D521:D525)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521:E525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521:F525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521:B525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521:C525," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G520" s="14" t="str">
         <f>'data'!$B$39</f>
@@ -17868,17 +17868,17 @@
         <f>'data'!$B$87</f>
       </c>
       <c r="J520" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L521:L525)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521:J525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521:K525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521:M525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521:N525," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K520" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521:J525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521:K525," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L520" s="18"/>
       <c r="M520" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521:M525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521:N525," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N520" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L521:L525)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521:M525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521:N525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521:J525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521:K525," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O520" s="14" t="str">
         <f>'data'!$B$86</f>
@@ -18037,17 +18037,17 @@
         <f>'data'!$B$41</f>
       </c>
       <c r="B528" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D529:D533)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529:B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529:C533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529:E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529:F533," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C528" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529:B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529:C533," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D528" s="18"/>
       <c r="E528" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529:E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529:F533," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F528" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D529:D533)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529:E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529:F533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529:B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529:C533," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G528" s="14" t="str">
         <f>'data'!$B$39</f>
@@ -18056,17 +18056,17 @@
         <f>'data'!$B$88</f>
       </c>
       <c r="J528" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L529:L533)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529:J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529:K533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529:M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529:N533," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K528" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529:J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529:K533," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L528" s="18"/>
       <c r="M528" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529:M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529:N533," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N528" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L529:L533)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529:M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529:N533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529:J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529:K533," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O528" s="14" t="str">
         <f>'data'!$B$86</f>
@@ -18225,17 +18225,17 @@
         <f>'data'!$B$41</f>
       </c>
       <c r="B536" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D537:D541)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537:B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537:C541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537:E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537:F541," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C536" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537:B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537:C541," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D536" s="18"/>
       <c r="E536" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537:E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537:F541," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F536" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D537:D541)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537:E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537:F541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537:B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537:C541," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G536" s="14" t="str">
         <f>'data'!$B$40</f>
@@ -18244,17 +18244,17 @@
         <f>'data'!$B$88</f>
       </c>
       <c r="J536" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L537:L541)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537:J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537:K541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537:M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537:N541," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K536" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537:J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537:K541," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L536" s="18"/>
       <c r="M536" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537:M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537:N541," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N536" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L537:L541)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537:M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537:N541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537:J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537:K541," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O536" s="14" t="str">
         <f>'data'!$B$87</f>
@@ -18783,17 +18783,17 @@
         <f>'data'!$B$43</f>
       </c>
       <c r="B563" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D564:D568)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564:B568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564:C568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564:E568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564:F568," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C563" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564:B568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564:C568," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D563" s="18"/>
       <c r="E563" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564:E568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564:F568," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F563" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D564:D568)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564:E568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564:F568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564:B568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564:C568," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G563" s="14" t="str">
         <f>'data'!$B$42</f>
@@ -18802,17 +18802,17 @@
         <f>'data'!$B$90</f>
       </c>
       <c r="J563" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L564:L568)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564:J568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564:K568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564:M568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564:N568," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K563" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564:J568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564:K568," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L563" s="18"/>
       <c r="M563" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564:M568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564:N568," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N563" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L564:L568)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564:M568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564:N568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564:J568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564:K568," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O563" s="14" t="str">
         <f>'data'!$B$89</f>
@@ -18971,17 +18971,17 @@
         <f>'data'!$B$44</f>
       </c>
       <c r="B571" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D572:D576)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572:B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572:C576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572:E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572:F576," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C571" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572:B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572:C576," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D571" s="18"/>
       <c r="E571" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572:E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572:F576," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F571" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D572:D576)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572:E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572:F576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572:B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572:C576," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G571" s="14" t="str">
         <f>'data'!$B$42</f>
@@ -18990,17 +18990,17 @@
         <f>'data'!$B$91</f>
       </c>
       <c r="J571" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L572:L576)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572:J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572:K576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572:M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572:N576," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K571" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572:J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572:K576," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L571" s="18"/>
       <c r="M571" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572:M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572:N576," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N571" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L572:L576)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572:M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572:N576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572:J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572:K576," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O571" s="14" t="str">
         <f>'data'!$B$89</f>
@@ -19159,17 +19159,17 @@
         <f>'data'!$B$44</f>
       </c>
       <c r="B579" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D580:D584)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580:B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580:C584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580:E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580:F584," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C579" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580:B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580:C584," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D579" s="18"/>
       <c r="E579" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580:E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580:F584," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F579" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D580:D584)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580:E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580:F584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580:B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580:C584," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G579" s="14" t="str">
         <f>'data'!$B$43</f>
@@ -19178,17 +19178,17 @@
         <f>'data'!$B$91</f>
       </c>
       <c r="J579" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L580:L584)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580:J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580:K584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580:M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580:N584," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K579" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580:J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580:K584," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L579" s="18"/>
       <c r="M579" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580:M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580:N584," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N579" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L580:L584)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580:M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580:N584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580:J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580:K584," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O579" s="14" t="str">
         <f>'data'!$B$90</f>
@@ -19717,17 +19717,17 @@
         <f>'data'!$B$46</f>
       </c>
       <c r="B606" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D607:D611)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607:B611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607:C611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607:E611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607:F611," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C606" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607:B611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607:C611," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D606" s="18"/>
       <c r="E606" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607:E611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607:F611," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F606" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D607:D611)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607:E611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607:F611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607:B611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607:C611," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G606" s="14" t="str">
         <f>'data'!$B$45</f>
@@ -19736,17 +19736,17 @@
         <f>'data'!$B$93</f>
       </c>
       <c r="J606" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L607:L611)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607:J611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607:K611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607:M611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607:N611," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K606" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607:J611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607:K611," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L606" s="18"/>
       <c r="M606" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607:M611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607:N611," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N606" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L607:L611)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607:M611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607:N611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607:J611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607:K611," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O606" s="14" t="str">
         <f>'data'!$B$92</f>
@@ -19892,17 +19892,17 @@
         <f>'data'!$B$47</f>
       </c>
       <c r="B614" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D615:D619)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615:B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615:C619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615:E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615:F619," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D615)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D616)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C614" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615:B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615:C619," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D614" s="18"/>
       <c r="E614" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615:E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615:F619," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F614" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D615:D619)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615:E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615:F619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615:B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615:C619," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D615)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D616)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G614" s="14" t="str">
         <f>'data'!$B$45</f>
@@ -19993,17 +19993,17 @@
         <f>'data'!$B$47</f>
       </c>
       <c r="B622" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D623:D627)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623:B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623:C627," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623:E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623:F627," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D623)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D624)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C622" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623:B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623:C627," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D622" s="18"/>
       <c r="E622" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623:E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623:F627," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F622" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D623:D627)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623:E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623:F627," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623:B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623:C627," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D623)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D624)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G622" s="14" t="str">
         <f>'data'!$B$46</f>
@@ -20419,17 +20419,17 @@
         <f>'data'!$B$49</f>
       </c>
       <c r="B649" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D650:D654)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650:B654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650:C654," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650:E654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650:F654," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D650)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D651)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D652)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D653)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D654)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C649" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650:B654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650:C654," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D649" s="18"/>
       <c r="E649" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650:E654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650:F654," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F649" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D650:D654)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650:E654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650:F654," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650:B654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650:C654," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D650)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D651)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D652)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D653)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D654)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G649" s="14" t="str">
         <f>'data'!$B$48</f>
@@ -20969,17 +20969,17 @@
         <v>348</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="14" t="s">
         <v>348</v>
@@ -20988,17 +20988,17 @@
         <v>348</v>
       </c>
       <c r="J12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L5:L9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5:M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5:N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5:J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5:K9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O12" s="14" t="s">
         <v>348</v>
@@ -21253,17 +21253,17 @@
         <v>348</v>
       </c>
       <c r="B28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G28" s="14" t="s">
         <v>348</v>
@@ -21272,17 +21272,17 @@
         <v>348</v>
       </c>
       <c r="J28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L28" s="14"/>
       <c r="M28" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N28" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L21:L25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21:M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21:N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21:J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21:K25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O28" s="14" t="s">
         <v>348</v>
@@ -21537,17 +21537,17 @@
         <v>348</v>
       </c>
       <c r="B44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D37:D41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37:E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37:F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37:B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37:C41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G44" s="14" t="s">
         <v>348</v>
@@ -21556,17 +21556,17 @@
         <v>348</v>
       </c>
       <c r="J44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L37:L41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37:J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37:K41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37:M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37:N41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37:J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37:K41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L44" s="14"/>
       <c r="M44" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37:M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37:N41," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N44" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L37:L41)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37:M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37:N41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37:J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37:K41," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O44" s="14" t="s">
         <v>348</v>
@@ -21821,17 +21821,17 @@
         <v>348</v>
       </c>
       <c r="B60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D53:D57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53:B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53:C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53:E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53:F57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53:B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53:C57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53:E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53:F57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D53:D57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53:E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53:F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53:B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53:C57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G60" s="14" t="s">
         <v>348</v>
@@ -21840,17 +21840,17 @@
         <v>348</v>
       </c>
       <c r="J60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L53:L57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53:J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53:K57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53:M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53:N57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53:J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53:K57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L60" s="14"/>
       <c r="M60" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53:M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53:N57," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N60" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L53:L57)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53:M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53:N57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53:J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53:K57," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O60" s="14" t="s">
         <v>348</v>
@@ -22105,17 +22105,17 @@
         <v>348</v>
       </c>
       <c r="B76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D69:D73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69:B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69:C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69:E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69:F73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69:B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69:C73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69:E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69:F73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D69:D73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69:E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69:F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69:B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69:C73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G76" s="14" t="s">
         <v>348</v>
@@ -22124,17 +22124,17 @@
         <v>348</v>
       </c>
       <c r="J76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L69:L73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69:J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69:K73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69:M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69:N73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69:J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69:K73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L76" s="14"/>
       <c r="M76" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69:M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69:N73," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N76" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L69:L73)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69:M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69:N73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69:J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69:K73," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O76" s="14" t="s">
         <v>348</v>
@@ -22389,17 +22389,17 @@
         <v>348</v>
       </c>
       <c r="B92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D85:D89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85:B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85:C89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85:E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85:F89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85:B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85:C89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D92" s="14"/>
       <c r="E92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85:E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85:F89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D85:D89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85:E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85:F89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85:B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85:C89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G92" s="14" t="s">
         <v>348</v>
@@ -22408,17 +22408,17 @@
         <v>348</v>
       </c>
       <c r="J92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L85:L89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85:J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85:K89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85:M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85:N89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85:J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85:K89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L92" s="14"/>
       <c r="M92" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85:M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85:N89," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N92" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L85:L89)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85:M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85:N89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85:J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85:K89," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O92" s="14" t="s">
         <v>348</v>
@@ -22673,17 +22673,17 @@
         <v>348</v>
       </c>
       <c r="B108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D101:D105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D101:D105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101:E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101:F105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101:B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101:C105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G108" s="14" t="s">
         <v>348</v>
@@ -22692,17 +22692,17 @@
         <v>348</v>
       </c>
       <c r="J108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L101:L105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L108" s="14"/>
       <c r="M108" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N108" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L101:L105)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101:M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101:N105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101:J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101:K105," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O108" s="14" t="s">
         <v>348</v>
@@ -22957,17 +22957,17 @@
         <v>348</v>
       </c>
       <c r="B124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D117:D121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D117:D121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117:E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117:F121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117:B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117:C121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G124" s="14" t="s">
         <v>348</v>
@@ -22976,17 +22976,17 @@
         <v>348</v>
       </c>
       <c r="J124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L117:L121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L124" s="14"/>
       <c r="M124" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N124" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L117:L121)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117:M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117:N121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117:J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117:K121," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O124" s="14" t="s">
         <v>348</v>
@@ -23241,17 +23241,17 @@
         <v>348</v>
       </c>
       <c r="B140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D133:D137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133:B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133:C137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133:E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133:F137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133:B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133:C137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133:E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133:F137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D133:D137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133:E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133:F137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133:B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133:C137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G140" s="14" t="s">
         <v>348</v>
@@ -23260,17 +23260,17 @@
         <v>348</v>
       </c>
       <c r="J140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L133:L137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133:J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133:K137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133:M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133:N137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133:J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133:K137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L140" s="14"/>
       <c r="M140" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133:M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133:N137," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N140" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L133:L137)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133:M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133:N137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133:J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133:K137," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O140" s="14" t="s">
         <v>348</v>
@@ -23525,17 +23525,17 @@
         <v>348</v>
       </c>
       <c r="B156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D149:D153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149:B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149:C153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149:E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149:F153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149:B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149:C153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D156" s="14"/>
       <c r="E156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149:E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149:F153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D149:D153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149:E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149:F153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149:B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149:C153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G156" s="14" t="s">
         <v>348</v>
@@ -23544,17 +23544,17 @@
         <v>348</v>
       </c>
       <c r="J156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L149:L153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149:J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149:K153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149:M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149:N153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149:J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149:K153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L156" s="14"/>
       <c r="M156" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149:M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149:N153," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N156" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L149:L153)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149:M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149:N153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149:J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149:K153," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O156" s="14" t="s">
         <v>348</v>
@@ -23809,17 +23809,17 @@
         <v>348</v>
       </c>
       <c r="B172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D165:D169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165:B169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165:C169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165:E169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165:F169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165:B169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165:C169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D172" s="14"/>
       <c r="E172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165:E169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165:F169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D165:D169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165:E169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165:F169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165:B169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165:C169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G172" s="14" t="s">
         <v>348</v>
@@ -23828,17 +23828,17 @@
         <v>348</v>
       </c>
       <c r="J172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L165:L169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165:J169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165:K169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165:M169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165:N169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165:J169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165:K169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L172" s="14"/>
       <c r="M172" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165:M169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165:N169," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N169," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N172" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L165:L169)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165:M169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165:N169," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165:J169," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165:K169," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L165)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N165," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J165," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K165," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L166)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N166," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J166," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K166," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L167)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N167," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J167," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K167," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L168)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N168," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J168," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K168," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L169)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N169," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J169," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K169," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O172" s="14" t="s">
         <v>348</v>
@@ -24093,17 +24093,17 @@
         <v>348</v>
       </c>
       <c r="B188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D181:D185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181:B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181:C185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181:E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181:F185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181:B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181:C185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D188" s="14"/>
       <c r="E188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181:E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181:F185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D181:D185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181:E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181:F185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181:B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181:C185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G188" s="14" t="s">
         <v>348</v>
@@ -24112,17 +24112,17 @@
         <v>348</v>
       </c>
       <c r="J188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L181:L185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181:J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181:K185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181:M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181:N185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181:J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181:K185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L188" s="14"/>
       <c r="M188" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181:M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181:N185," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N188" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L181:L185)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181:M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181:N185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181:J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181:K185," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L182)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N182," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J182," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K182," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L183)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N183," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J183," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K183," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L184)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N184," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J184," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K184," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O188" s="14" t="s">
         <v>348</v>
@@ -24377,17 +24377,17 @@
         <v>348</v>
       </c>
       <c r="B204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D197:D201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197:B201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197:C201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197:E201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197:F201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197:B201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197:C201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D204" s="14"/>
       <c r="E204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197:E201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197:F201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D197:D201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197:E201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197:F201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197:B201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197:C201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G204" s="14" t="s">
         <v>348</v>
@@ -24396,17 +24396,17 @@
         <v>348</v>
       </c>
       <c r="J204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L197:L201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197:J201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197:K201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197:M201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197:N201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197:J201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197:K201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L204" s="14"/>
       <c r="M204" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197:M201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197:N201," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N201," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N204" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L197:L201)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197:M201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197:N201," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197:J201," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197:K201," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L198)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N198," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J198," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K198," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L199)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N199," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J199," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K199," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L200)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N200," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J200," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K200," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L201)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N201," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J201," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K201," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O204" s="14" t="s">
         <v>348</v>
@@ -24661,17 +24661,17 @@
         <v>348</v>
       </c>
       <c r="B220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D213:D217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213:B217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213:C217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213:E217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213:F217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213:B217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213:C217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D220" s="14"/>
       <c r="E220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213:E217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213:F217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D213:D217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213:E217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213:F217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213:B217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213:C217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G220" s="14" t="s">
         <v>348</v>
@@ -24680,17 +24680,17 @@
         <v>348</v>
       </c>
       <c r="J220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L213:L217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213:J217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213:K217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213:M217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213:N217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213:J217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213:K217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L220" s="14"/>
       <c r="M220" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213:M217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213:N217," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N217," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N220" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L213:L217)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213:M217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213:N217," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213:J217," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213:K217," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L213)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N213," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J213," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K213," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L214)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N214," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J214," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K214," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L215)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N215," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J215," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K215," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L216)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N216," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J216," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K216," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L217)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N217," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J217," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K217," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O220" s="14" t="s">
         <v>348</v>
@@ -24945,17 +24945,17 @@
         <v>348</v>
       </c>
       <c r="B236" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D229:D233)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229:B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229:C233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229:E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229:F233," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C236" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229:B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229:C233," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D236" s="14"/>
       <c r="E236" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229:E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229:F233," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F236" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D229:D233)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229:E233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229:F233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229:B233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229:C233," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C233," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G236" s="14" t="s">
         <v>348</v>
@@ -24964,17 +24964,17 @@
         <v>348</v>
       </c>
       <c r="J236" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L229:L233)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229:J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229:K233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229:M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229:N233," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K236" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229:J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229:K233," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L236" s="14"/>
       <c r="M236" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229:M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229:N233," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N236" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L229:L233)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229:M233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229:N233," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229:J233," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229:K233," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L233)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N233," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J233," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K233," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O236" s="14" t="s">
         <v>348</v>
@@ -25229,17 +25229,17 @@
         <v>348</v>
       </c>
       <c r="B257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D250:D254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250:B254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250:C254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250:E254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250:F254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250:B254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250:C254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D257" s="14"/>
       <c r="E257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250:E254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250:F254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D250:D254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250:E254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250:F254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250:B254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250:C254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G257" s="14" t="s">
         <v>348</v>
@@ -25248,17 +25248,17 @@
         <v>348</v>
       </c>
       <c r="J257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L250:L254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250:J254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250:K254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250:M254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250:N254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250:J254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250:K254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L257" s="14"/>
       <c r="M257" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250:M254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250:N254," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N254," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N257" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L250:L254)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250:M254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250:N254," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250:J254," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250:K254," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L250)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N250," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J250," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K250," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L251)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N251," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J251," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K251," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L252)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N252," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J252," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K252," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L253)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N253," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J253," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K253," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L254)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N254," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J254," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K254," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O257" s="14" t="s">
         <v>348</v>
@@ -25513,17 +25513,17 @@
         <v>348</v>
       </c>
       <c r="B273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D266:D270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266:B270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266:C270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266:E270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266:F270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266:B270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266:C270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D273" s="14"/>
       <c r="E273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266:E270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266:F270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D266:D270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266:E270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266:F270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266:B270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266:C270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G273" s="14" t="s">
         <v>348</v>
@@ -25532,17 +25532,17 @@
         <v>348</v>
       </c>
       <c r="J273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L266:L270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266:J270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266:K270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266:M270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266:N270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266:J270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266:K270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L273" s="14"/>
       <c r="M273" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266:M270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266:N270," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N270," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N273" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L266:L270)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266:M270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266:N270," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266:J270," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266:K270," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L268)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N268," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J268," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K268," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L269)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N269," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J269," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K269," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L270)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N270," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J270," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K270," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O273" s="14" t="s">
         <v>348</v>
@@ -25797,17 +25797,17 @@
         <v>348</v>
       </c>
       <c r="B289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D282:D286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282:B286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282:C286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282:E286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282:F286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282:B286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282:C286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D289" s="14"/>
       <c r="E289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282:E286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282:F286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D282:D286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282:E286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282:F286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282:B286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282:C286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G289" s="14" t="s">
         <v>348</v>
@@ -25816,17 +25816,17 @@
         <v>348</v>
       </c>
       <c r="J289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L282:L286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282:J286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282:K286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282:M286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282:N286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282:J286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282:K286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L289" s="14"/>
       <c r="M289" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282:M286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282:N286," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N286," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N289" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L282:L286)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282:M286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282:N286," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282:J286," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282:K286," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L284)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N284," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J284," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K284," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L285)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N285," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J285," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K285," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L286)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N286," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J286," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K286," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O289" s="14" t="s">
         <v>348</v>
@@ -26081,17 +26081,17 @@
         <v>348</v>
       </c>
       <c r="B305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D298:D302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298:B302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298:C302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298:E302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298:F302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298:B302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298:C302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D305" s="14"/>
       <c r="E305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298:E302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298:F302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D298:D302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298:E302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298:F302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298:B302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298:C302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G305" s="14" t="s">
         <v>348</v>
@@ -26100,17 +26100,17 @@
         <v>348</v>
       </c>
       <c r="J305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L298:L302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298:J302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298:K302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298:M302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298:N302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298:J302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298:K302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L305" s="14"/>
       <c r="M305" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298:M302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298:N302," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N302," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N305" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L298:L302)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298:M302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298:N302," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298:J302," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298:K302," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L298)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N298," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J298," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K298," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L299)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N299," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J299," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K299," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L300)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N300," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J300," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K300," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L301)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N301," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J301," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K301," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L302)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N302," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J302," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K302," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O305" s="14" t="s">
         <v>348</v>
@@ -26365,17 +26365,17 @@
         <v>348</v>
       </c>
       <c r="B321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D314:D318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D321" s="14"/>
       <c r="E321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D314:D318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314:E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314:F318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314:B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314:C318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G321" s="14" t="s">
         <v>348</v>
@@ -26384,17 +26384,17 @@
         <v>348</v>
       </c>
       <c r="J321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L314:L318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L321" s="14"/>
       <c r="M321" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N321" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L314:L318)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314:M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314:N318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314:J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314:K318," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O321" s="14" t="s">
         <v>348</v>
@@ -26649,17 +26649,17 @@
         <v>348</v>
       </c>
       <c r="B337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D330:D334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330:B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330:C334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330:E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330:F334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330:B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330:C334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D337" s="14"/>
       <c r="E337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330:E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330:F334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D330:D334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330:E334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330:F334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330:B334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330:C334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G337" s="14" t="s">
         <v>348</v>
@@ -26668,17 +26668,17 @@
         <v>348</v>
       </c>
       <c r="J337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L330:L334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330:J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330:K334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330:M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330:N334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330:J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330:K334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L337" s="14"/>
       <c r="M337" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330:M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330:N334," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N337" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L330:L334)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330:M334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330:N334," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330:J334," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330:K334," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L330)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N330," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J330," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K330," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L331)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N331," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J331," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K331," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L332)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N332," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J332," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K332," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L333)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N333," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J333," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K333," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L334)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N334," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J334," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K334," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O337" s="14" t="s">
         <v>348</v>
@@ -26933,17 +26933,17 @@
         <v>348</v>
       </c>
       <c r="B353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D346:D350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346:B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346:C350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346:E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346:F350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346:B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346:C350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D353" s="14"/>
       <c r="E353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346:E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346:F350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D346:D350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346:E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346:F350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346:B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346:C350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G353" s="14" t="s">
         <v>348</v>
@@ -26952,17 +26952,17 @@
         <v>348</v>
       </c>
       <c r="J353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L346:L350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346:J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346:K350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346:M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346:N350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346:J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346:K350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L353" s="14"/>
       <c r="M353" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346:M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346:N350," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N353" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L346:L350)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346:M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346:N350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346:J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346:K350," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L346)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N346," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J346," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K346," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L347)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N347," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J347," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K347," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L348)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N348," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J348," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K348," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O353" s="14" t="s">
         <v>348</v>
@@ -27217,17 +27217,17 @@
         <v>348</v>
       </c>
       <c r="B369" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D362:D366)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362:B366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362:C366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362:E366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362:F366," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D364)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C364," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F364," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C369" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362:B366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362:C366," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D369" s="14"/>
       <c r="E369" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362:E366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362:F366," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F369" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D362:D366)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362:E366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362:F366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362:B366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362:C366," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C363," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D364)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F364," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C364," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G369" s="14" t="s">
         <v>348</v>
@@ -27236,17 +27236,17 @@
         <v>348</v>
       </c>
       <c r="J369" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L362:L366)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362:J366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362:K366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362:M366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362:N366," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L364)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K364," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N364," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K369" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362:J366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362:K366," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L369" s="14"/>
       <c r="M369" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362:M366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362:N366," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N369" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L362:L366)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362:M366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362:N366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362:J366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362:K366," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L362)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N362," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J362," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K362," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L363)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N363," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J363," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K363," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L364)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N364," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J364," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K364," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O369" s="14" t="s">
         <v>348</v>
@@ -27501,17 +27501,17 @@
         <v>348</v>
       </c>
       <c r="B390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D383:D387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383:B387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383:C387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383:E387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383:F387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383:B387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383:C387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D390" s="14"/>
       <c r="E390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383:E387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383:F387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D383:D387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383:E387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383:F387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383:B387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383:C387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G390" s="14" t="s">
         <v>348</v>
@@ -27520,17 +27520,17 @@
         <v>348</v>
       </c>
       <c r="J390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L383:L387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383:J387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383:K387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383:M387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383:N387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383:J387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383:K387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L390" s="14"/>
       <c r="M390" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383:M387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383:N387," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N387," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N390" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L383:L387)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383:M387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383:N387," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383:J387," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383:K387," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L383)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N383," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J383," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K383," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L384)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N384," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J384," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K384," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L385)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N385," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J385," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K385," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L386)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N386," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J386," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K386," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L387)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N387," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J387," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K387," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O390" s="14" t="s">
         <v>348</v>
@@ -27785,17 +27785,17 @@
         <v>348</v>
       </c>
       <c r="B406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D399:D403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399:B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399:C403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399:E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399:F403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399:B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399:C403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D406" s="14"/>
       <c r="E406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399:E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399:F403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D399:D403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399:E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399:F403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399:B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399:C403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G406" s="14" t="s">
         <v>348</v>
@@ -27804,17 +27804,17 @@
         <v>348</v>
       </c>
       <c r="J406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L399:L403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399:J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399:K403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399:M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399:N403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399:J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399:K403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L406" s="14"/>
       <c r="M406" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399:M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399:N403," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N406" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L399:L403)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399:M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399:N403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399:J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399:K403," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L399)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N399," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J399," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K399," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O406" s="14" t="s">
         <v>348</v>
@@ -28069,17 +28069,17 @@
         <v>348</v>
       </c>
       <c r="B422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D415:D419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415:B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415:C419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415:E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415:F419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415:B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415:C419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D422" s="14"/>
       <c r="E422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415:E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415:F419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D415:D419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415:E419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415:F419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415:B419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415:C419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G422" s="14" t="s">
         <v>348</v>
@@ -28088,17 +28088,17 @@
         <v>348</v>
       </c>
       <c r="J422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L415:L419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415:J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415:K419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415:M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415:N419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415:J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415:K419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L422" s="14"/>
       <c r="M422" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415:M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415:N419," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N422" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L415:L419)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415:M419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415:N419," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415:J419," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415:K419," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L415)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N415," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J415," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K415," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L416)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N416," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J416," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K416," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L417)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N417," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J417," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K417," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L418)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N418," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J418," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K418," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L419)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N419," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J419," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K419," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O422" s="14" t="s">
         <v>348</v>
@@ -28353,17 +28353,17 @@
         <v>348</v>
       </c>
       <c r="B438" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D431:D435)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B431:B435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C431:C435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E431:E435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F431:F435," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D431)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C431," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F431," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D432)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C432," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F432," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D433)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C433," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F433," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D434)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C434," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F434," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C438" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B431:B435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C431:C435," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D438" s="14"/>
       <c r="E438" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E431:E435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F431:F435," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F438" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D431:D435)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E431:E435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F431:F435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B431:B435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C431:C435," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D431)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F431," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C431," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D432)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F432," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C432," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D433)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F433," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C433," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D434)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F434," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C434," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G438" s="14" t="s">
         <v>348</v>
@@ -28372,17 +28372,17 @@
         <v>348</v>
       </c>
       <c r="J438" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L431:L435)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J431:J435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K431:K435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M431:M435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N431:N435," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L431)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K431," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N431," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L432)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K432," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N432," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L433)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K433," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N433," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L434)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K434," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N434," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K438" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J431:J435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K431:K435," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L438" s="14"/>
       <c r="M438" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M431:M435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N431:N435," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N438" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L431:L435)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M431:M435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N431:N435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J431:J435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K431:K435," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L431)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N431," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J431," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K431," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L432)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N432," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J432," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K432," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L433)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N433," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J433," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K433," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L434)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N434," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J434," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K434," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O438" s="14" t="s">
         <v>348</v>
@@ -28637,17 +28637,17 @@
         <v>348</v>
       </c>
       <c r="B459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D452:D456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452:B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452:C456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452:E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452:F456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452:B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452:C456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D459" s="14"/>
       <c r="E459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452:E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452:F456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D452:D456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452:E456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452:F456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452:B456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452:C456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G459" s="14" t="s">
         <v>348</v>
@@ -28656,17 +28656,17 @@
         <v>348</v>
       </c>
       <c r="J459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L452:L456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452:J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452:K456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452:M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452:N456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452:J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452:K456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L459" s="14"/>
       <c r="M459" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452:M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452:N456," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N459" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L452:L456)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452:M456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452:N456," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452:J456," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452:K456," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L456)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N456," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J456," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K456," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O459" s="14" t="s">
         <v>348</v>
@@ -28921,17 +28921,17 @@
         <v>348</v>
       </c>
       <c r="B475" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D468:D472)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B468:B472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C468:C472," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E468:E472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F468:F472," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D468)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C468," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F468," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D469)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C469," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F469," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D470)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C470," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F470," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D471)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C471," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F471," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D472)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C472," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F472," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C475" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B468:B472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C468:C472," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C472," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D475" s="14"/>
       <c r="E475" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E468:E472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F468:F472," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F472," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F475" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D468:D472)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E468:E472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F468:F472," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B468:B472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C468:C472," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D468)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F468," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C468," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D469)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F469," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C469," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D470)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F470," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C470," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D471)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F471," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C471," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D472)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F472," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C472," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G475" s="14" t="s">
         <v>348</v>
@@ -28940,17 +28940,17 @@
         <v>348</v>
       </c>
       <c r="J475" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L468:L472)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J468:J472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K468:K472," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M468:M472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N468:N472," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L468)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K468," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N468," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L469)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K469," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N469," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L470)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K470," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N470," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L471)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K471," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N471," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L472)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K472," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N472," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K475" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J468:J472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K468:K472," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K472," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L475" s="14"/>
       <c r="M475" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M468:M472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N468:N472," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N472," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N475" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L468:L472)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M468:M472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N468:N472," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J468:J472," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K468:K472," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L468)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N468," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J468," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K468," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L469)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N469," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J469," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K469," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L470)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N470," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J470," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K470," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L471)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N471," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J471," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K471," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L472)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N472," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J472," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K472," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O475" s="14" t="s">
         <v>348</v>
@@ -29205,17 +29205,17 @@
         <v>348</v>
       </c>
       <c r="B496" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D489:D493)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489:B493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489:C493," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489:E493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489:F493," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D493)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C493," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F493," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C496" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489:B493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489:C493," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C493," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D496" s="14"/>
       <c r="E496" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489:E493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489:F493," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F493," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F496" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D489:D493)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489:E493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489:F493," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489:B493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489:C493," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C492," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D493)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F493," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C493," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G496" s="14" t="s">
         <v>348</v>
@@ -29224,17 +29224,17 @@
         <v>348</v>
       </c>
       <c r="J496" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L489:L493)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489:J493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489:K493," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489:M493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489:N493," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L493)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K493," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N493," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="K496" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489:J493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489:K493," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K493," ",""),"0",""),"-","")) </f>
       </c>
       <c r="L496" s="14"/>
       <c r="M496" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489:M493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489:N493," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N493," ",""),"0",""),"-","")) </f>
       </c>
       <c r="N496" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(L489:L493)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489:M493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489:N493," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489:J493," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489:K493," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L491)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N491," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J491," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K491," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L492)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N492," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J492," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K492," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L493)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N493," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J493," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K493," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="O496" s="14" t="s">
         <v>348</v>
@@ -29386,17 +29386,17 @@
         <v>348</v>
       </c>
       <c r="B517" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D510:D514)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B510:B514," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C510:C514," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E510:E514," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F510:F514," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D510)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C510," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F510," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D511)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C511," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F511," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D512)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C512," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F512," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D513)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C513," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F513," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D514)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B514," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C514," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E514," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F514," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C517" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B510:B514," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C510:C514," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B514," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C514," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D517" s="14"/>
       <c r="E517" s="14" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E510:E514," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F510:F514," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E514," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F514," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F517" s="14" t="str">
-        <f>SUMPRODUCT((UPPER(D510:D514)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E510:E514," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F510:F514," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B510:B514," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C510:C514," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D510)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F510," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B510," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C510," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D511)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F511," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B511," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C511," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D512)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F512," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B512," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C512," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D513)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F513," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B513," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C513," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D514)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E514," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F514," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B514," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C514," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G517" s="14" t="s">
         <v>348</v>

--- a/pools-example-large-teams-max-size.xlsx
+++ b/pools-example-large-teams-max-size.xlsx
@@ -6641,17 +6641,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F4" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G4" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -6660,17 +6660,17 @@
         <f>'data'!$B$51</f>
       </c>
       <c r="J4" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L4" s="18"/>
       <c r="M4" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N4" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O4" s="14" t="str">
         <f>'data'!$B$50</f>
@@ -6829,17 +6829,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B12" s="14" t="str">
-        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="str">
         <f>'data'!$B$3</f>
@@ -6848,17 +6848,17 @@
         <f>'data'!$B$52</f>
       </c>
       <c r="J12" s="14" t="str">
-        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L13)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N13," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J13," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L14)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N14," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J14," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K14," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L15)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N15," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J15," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K15," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L16)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N16," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J16," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K16," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L17)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N17," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J17," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K17," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="str">
         <f>'data'!$B$50</f>
@@ -7017,17 +7017,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="B20" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F20" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G20" s="14" t="str">
         <f>'data'!$B$4</f>
@@ -7036,17 +7036,17 @@
         <f>'data'!$B$52</f>
       </c>
       <c r="J20" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L20" s="18"/>
       <c r="M20" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N20" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O20" s="14" t="str">
         <f>'data'!$B$51</f>
@@ -7575,17 +7575,17 @@
         <f>'data'!$B$7</f>
       </c>
       <c r="B47" s="14" t="str">
-        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C47" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F47" s="14" t="str">
-        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G47" s="14" t="str">
         <f>'data'!$B$6</f>
@@ -7594,17 +7594,17 @@
         <f>'data'!$B$54</f>
       </c>
       <c r="J47" s="14" t="str">
-        <f>IF(UPPER(L48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K47" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L47" s="18"/>
       <c r="M47" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N47" s="14" t="str">
-        <f>IF(UPPER(L48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L48)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N48," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J48," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K48," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L49)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N49," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J49," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K49," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L50)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N50," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K50," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L51)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N51," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K51," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L52)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O47" s="14" t="str">
         <f>'data'!$B$53</f>
@@ -7763,17 +7763,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B55" s="14" t="str">
-        <f>IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C55" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F55" s="14" t="str">
-        <f>IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G55" s="14" t="str">
         <f>'data'!$B$6</f>
@@ -7782,17 +7782,17 @@
         <f>'data'!$B$55</f>
       </c>
       <c r="J55" s="14" t="str">
-        <f>IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K55" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L55" s="18"/>
       <c r="M55" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N55" s="14" t="str">
-        <f>IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K60," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O55" s="14" t="str">
         <f>'data'!$B$53</f>
@@ -7951,17 +7951,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B63" s="14" t="str">
-        <f>IF(UPPER(D64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C63" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F63" s="14" t="str">
-        <f>IF(UPPER(D64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F64," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C64," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F65," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C65," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C68," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G63" s="14" t="str">
         <f>'data'!$B$7</f>
@@ -7970,17 +7970,17 @@
         <f>'data'!$B$55</f>
       </c>
       <c r="J63" s="14" t="str">
-        <f>IF(UPPER(L64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K63" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L63" s="18"/>
       <c r="M63" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N63" s="14" t="str">
-        <f>IF(UPPER(L64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L64)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N64," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J64," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K64," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L65)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N65," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J65," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K65," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L66)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N66," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J66," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K66," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L67)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N67," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J67," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K67," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L68)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N68," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J68," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K68," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O63" s="14" t="str">
         <f>'data'!$B$54</f>
@@ -8509,17 +8509,17 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="B90" s="14" t="str">
-        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F90" s="14" t="str">
-        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C95," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G90" s="14" t="str">
         <f>'data'!$B$9</f>
@@ -8528,17 +8528,17 @@
         <f>'data'!$B$57</f>
       </c>
       <c r="J90" s="14" t="str">
-        <f>IF(UPPER(L91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L90" s="18"/>
       <c r="M90" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N90" s="14" t="str">
-        <f>IF(UPPER(L91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K94," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L95)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N95," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J95," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K95," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O90" s="14" t="str">
         <f>'data'!$B$56</f>
@@ -8697,17 +8697,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B98" s="14" t="str">
-        <f>IF(UPPER(D99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C98" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D98" s="18"/>
       <c r="E98" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F98" s="14" t="str">
-        <f>IF(UPPER(D99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F99," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C99," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F100," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C100," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G98" s="14" t="str">
         <f>'data'!$B$9</f>
@@ -8716,17 +8716,17 @@
         <f>'data'!$B$58</f>
       </c>
       <c r="J98" s="14" t="str">
-        <f>IF(UPPER(L99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K98" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L98" s="18"/>
       <c r="M98" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N98" s="14" t="str">
-        <f>IF(UPPER(L99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L99)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N99," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J99," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K99," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L100)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N100," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J100," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K100," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O98" s="14" t="str">
         <f>'data'!$B$56</f>
@@ -8885,17 +8885,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="B106" s="14" t="str">
-        <f>IF(UPPER(D107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C106" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D106" s="18"/>
       <c r="E106" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F106" s="14" t="str">
-        <f>IF(UPPER(D107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F107," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C107," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F108," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C108," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G106" s="14" t="str">
         <f>'data'!$B$10</f>
@@ -8904,17 +8904,17 @@
         <f>'data'!$B$58</f>
       </c>
       <c r="J106" s="14" t="str">
-        <f>IF(UPPER(L107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K106" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L106" s="18"/>
       <c r="M106" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N106" s="14" t="str">
-        <f>IF(UPPER(L107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L107)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N107," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J107," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K107," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L108)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N108," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J108," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K108," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L109)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N109," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J109," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K109," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L110)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N110," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J110," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K110," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K111," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O106" s="14" t="str">
         <f>'data'!$B$57</f>
@@ -9443,17 +9443,17 @@
         <f>'data'!$B$13</f>
       </c>
       <c r="B133" s="14" t="str">
-        <f>IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C133" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D133" s="18"/>
       <c r="E133" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F133" s="14" t="str">
-        <f>IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C138," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G133" s="14" t="str">
         <f>'data'!$B$12</f>
@@ -9462,17 +9462,17 @@
         <f>'data'!$B$60</f>
       </c>
       <c r="J133" s="14" t="str">
-        <f>IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K133" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L133" s="18"/>
       <c r="M133" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N133" s="14" t="str">
-        <f>IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L138)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N138," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J138," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K138," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O133" s="14" t="str">
         <f>'data'!$B$59</f>
@@ -9631,17 +9631,17 @@
         <f>'data'!$B$14</f>
       </c>
       <c r="B141" s="14" t="str">
-        <f>IF(UPPER(D142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C141" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D141" s="18"/>
       <c r="E141" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F141" s="14" t="str">
-        <f>IF(UPPER(D142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F142," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C142," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F143," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C143," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C146," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G141" s="14" t="str">
         <f>'data'!$B$12</f>
@@ -9650,17 +9650,17 @@
         <f>'data'!$B$61</f>
       </c>
       <c r="J141" s="14" t="str">
-        <f>IF(UPPER(L142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K141" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L141" s="18"/>
       <c r="M141" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N141" s="14" t="str">
-        <f>IF(UPPER(L142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L142)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N142," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J142," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K142," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L143)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N143," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J143," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K143," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L144)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N144," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J144," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K144," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L145)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N145," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J145," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K145," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L146)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N146," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J146," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K146," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O141" s="14" t="str">
         <f>'data'!$B$59</f>
@@ -9819,17 +9819,17 @@
         <f>'data'!$B$14</f>
       </c>
       <c r="B149" s="14" t="str">
-        <f>IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C149" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D149" s="18"/>
       <c r="E149" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F149" s="14" t="str">
-        <f>IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C154," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G149" s="14" t="str">
         <f>'data'!$B$13</f>
@@ -9838,17 +9838,17 @@
         <f>'data'!$B$61</f>
       </c>
       <c r="J149" s="14" t="str">
-        <f>IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K149" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L149" s="18"/>
       <c r="M149" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N149" s="14" t="str">
-        <f>IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K152," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L153)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N153," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J153," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K153," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L154)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N154," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J154," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K154," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O149" s="14" t="str">
         <f>'data'!$B$60</f>
@@ -10377,17 +10377,17 @@
         <f>'data'!$B$16</f>
       </c>
       <c r="B176" s="14" t="str">
-        <f>IF(UPPER(D177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C176" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D176" s="18"/>
       <c r="E176" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F176" s="14" t="str">
-        <f>IF(UPPER(D177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F177," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C177," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F178," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C178," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F179," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C179," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F180," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C180," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C181," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G176" s="14" t="str">
         <f>'data'!$B$15</f>
@@ -10396,17 +10396,17 @@
         <f>'data'!$B$63</f>
       </c>
       <c r="J176" s="14" t="str">
-        <f>IF(UPPER(L177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K176" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L176" s="18"/>
       <c r="M176" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N176" s="14" t="str">
-        <f>IF(UPPER(L177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L177)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N177," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J177," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K177," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L178)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N178," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J178," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K178," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L179)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N179," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J179," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K179," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L180)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N180," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J180," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K180," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L181)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N181," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J181," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K181," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O176" s="14" t="str">
         <f>'data'!$B$62</f>
@@ -10565,17 +10565,17 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="B184" s="14" t="str">
-        <f>IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C184" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D184" s="18"/>
       <c r="E184" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F184" s="14" t="str">
-        <f>IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C185," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F186," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C186," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C189," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G184" s="14" t="str">
         <f>'data'!$B$15</f>
@@ -10584,17 +10584,17 @@
         <f>'data'!$B$64</f>
       </c>
       <c r="J184" s="14" t="str">
-        <f>IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K184" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L184" s="18"/>
       <c r="M184" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N184" s="14" t="str">
-        <f>IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L185)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N185," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J185," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K185," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L186)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N186," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J186," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K186," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L187)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N187," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J187," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K187," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L188)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N188," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J188," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K188," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L189)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N189," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J189," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K189," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O184" s="14" t="str">
         <f>'data'!$B$62</f>
@@ -10753,17 +10753,17 @@
         <f>'data'!$B$17</f>
       </c>
       <c r="B192" s="14" t="str">
-        <f>IF(UPPER(D193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C192" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D192" s="18"/>
       <c r="E192" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F192" s="14" t="str">
-        <f>IF(UPPER(D193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F193," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C193," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F194," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C194," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C197," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G192" s="14" t="str">
         <f>'data'!$B$16</f>
@@ -10772,17 +10772,17 @@
         <f>'data'!$B$64</f>
       </c>
       <c r="J192" s="14" t="str">
-        <f>IF(UPPER(L193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K192" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L192" s="18"/>
       <c r="M192" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N192" s="14" t="str">
-        <f>IF(UPPER(L193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L193)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N193," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J193," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K193," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L194)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N194," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J194," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K194," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L195)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N195," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J195," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K195," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L196)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N196," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J196," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K196," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L197)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N197," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J197," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K197," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O192" s="14" t="str">
         <f>'data'!$B$63</f>
@@ -11311,17 +11311,17 @@
         <f>'data'!$B$19</f>
       </c>
       <c r="B219" s="14" t="str">
-        <f>IF(UPPER(D220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C219" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D219" s="18"/>
       <c r="E219" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F219" s="14" t="str">
-        <f>IF(UPPER(D220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F220," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C220," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F221," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C221," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F222," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C222," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F223," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C223," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C224," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G219" s="14" t="str">
         <f>'data'!$B$18</f>
@@ -11330,17 +11330,17 @@
         <f>'data'!$B$66</f>
       </c>
       <c r="J219" s="14" t="str">
-        <f>IF(UPPER(L220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K219" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L219" s="18"/>
       <c r="M219" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N219" s="14" t="str">
-        <f>IF(UPPER(L220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L220)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N220," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J220," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K220," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L221)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N221," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J221," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K221," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L222)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N222," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J222," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K222," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L223)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N223," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J223," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K223," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L224)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N224," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J224," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K224," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O219" s="14" t="str">
         <f>'data'!$B$65</f>
@@ -11499,17 +11499,17 @@
         <f>'data'!$B$20</f>
       </c>
       <c r="B227" s="14" t="str">
-        <f>IF(UPPER(D228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C227" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D227" s="18"/>
       <c r="E227" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F227" s="14" t="str">
-        <f>IF(UPPER(D228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F228," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C228," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C232," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G227" s="14" t="str">
         <f>'data'!$B$18</f>
@@ -11518,17 +11518,17 @@
         <f>'data'!$B$67</f>
       </c>
       <c r="J227" s="14" t="str">
-        <f>IF(UPPER(L228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K227" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L227" s="18"/>
       <c r="M227" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N227" s="14" t="str">
-        <f>IF(UPPER(L228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L228)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N228," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J228," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K228," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L229)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N229," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J229," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K229," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L230)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N230," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J230," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K230," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L231)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N231," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J231," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K231," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L232)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N232," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J232," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K232," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O227" s="14" t="str">
         <f>'data'!$B$65</f>
@@ -11687,17 +11687,17 @@
         <f>'data'!$B$20</f>
       </c>
       <c r="B235" s="14" t="str">
-        <f>IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C235" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D235" s="18"/>
       <c r="E235" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F235" s="14" t="str">
-        <f>IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C240," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G235" s="14" t="str">
         <f>'data'!$B$19</f>
@@ -11706,17 +11706,17 @@
         <f>'data'!$B$67</f>
       </c>
       <c r="J235" s="14" t="str">
-        <f>IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K235" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L235" s="18"/>
       <c r="M235" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N235" s="14" t="str">
-        <f>IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L236)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N236," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J236," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K236," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L237)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N237," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J237," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K237," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L238)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N238," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J238," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K238," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L239)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N239," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J239," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K239," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L240)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N240," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J240," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K240," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O235" s="14" t="str">
         <f>'data'!$B$66</f>
@@ -12245,17 +12245,17 @@
         <f>'data'!$B$22</f>
       </c>
       <c r="B262" s="14" t="str">
-        <f>IF(UPPER(D263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C262" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D262" s="18"/>
       <c r="E262" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F262" s="14" t="str">
-        <f>IF(UPPER(D263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F263," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C263," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F264," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C264," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F265," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C265," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F266," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C266," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C267," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G262" s="14" t="str">
         <f>'data'!$B$21</f>
@@ -12264,17 +12264,17 @@
         <f>'data'!$B$69</f>
       </c>
       <c r="J262" s="14" t="str">
-        <f>IF(UPPER(L263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K262" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L262" s="18"/>
       <c r="M262" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N262" s="14" t="str">
-        <f>IF(UPPER(L263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L263)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N263," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J263," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K263," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L264)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N264," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J264," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K264," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L265)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N265," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J265," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K265," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L266)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N266," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J266," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K266," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L267)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N267," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J267," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K267," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O262" s="14" t="str">
         <f>'data'!$B$68</f>
@@ -12433,17 +12433,17 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="B270" s="14" t="str">
-        <f>IF(UPPER(D271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C270" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D270" s="18"/>
       <c r="E270" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F270" s="14" t="str">
-        <f>IF(UPPER(D271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F271," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C271," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F272," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C272," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C275," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G270" s="14" t="str">
         <f>'data'!$B$21</f>
@@ -12452,17 +12452,17 @@
         <f>'data'!$B$70</f>
       </c>
       <c r="J270" s="14" t="str">
-        <f>IF(UPPER(L271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K270" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L270" s="18"/>
       <c r="M270" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N270" s="14" t="str">
-        <f>IF(UPPER(L271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L271)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N271," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J271," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K271," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L272)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N272," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J272," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K272," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L273)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N273," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J273," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K273," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L274)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N274," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J274," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K274," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L275)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N275," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J275," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K275," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O270" s="14" t="str">
         <f>'data'!$B$68</f>
@@ -12621,17 +12621,17 @@
         <f>'data'!$B$23</f>
       </c>
       <c r="B278" s="14" t="str">
-        <f>IF(UPPER(D279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C278" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D278" s="18"/>
       <c r="E278" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F278" s="14" t="str">
-        <f>IF(UPPER(D279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F279," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C279," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F280," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C280," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C283," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G278" s="14" t="str">
         <f>'data'!$B$22</f>
@@ -12640,17 +12640,17 @@
         <f>'data'!$B$70</f>
       </c>
       <c r="J278" s="14" t="str">
-        <f>IF(UPPER(L279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K278" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L278" s="18"/>
       <c r="M278" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N278" s="14" t="str">
-        <f>IF(UPPER(L279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L279)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N279," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J279," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K279," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L280)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N280," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J280," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K280," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L281)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N281," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J281," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K281," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L282)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N282," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J282," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K282," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L283)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N283," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J283," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K283," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O278" s="14" t="str">
         <f>'data'!$B$69</f>
@@ -13179,17 +13179,17 @@
         <f>'data'!$B$25</f>
       </c>
       <c r="B305" s="14" t="str">
-        <f>IF(UPPER(D306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C305" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D305" s="18"/>
       <c r="E305" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F305" s="14" t="str">
-        <f>IF(UPPER(D306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F306," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C306," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F307," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C307," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F308," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C308," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F309," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C309," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C310," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G305" s="14" t="str">
         <f>'data'!$B$24</f>
@@ -13198,17 +13198,17 @@
         <f>'data'!$B$72</f>
       </c>
       <c r="J305" s="14" t="str">
-        <f>IF(UPPER(L306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K305" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L305" s="18"/>
       <c r="M305" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N305" s="14" t="str">
-        <f>IF(UPPER(L306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L306)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N306," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J306," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K306," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L307)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N307," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J307," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K307," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L308)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N308," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J308," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K308," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L309)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N309," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J309," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K309," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L310)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N310," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J310," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K310," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O305" s="14" t="str">
         <f>'data'!$B$71</f>
@@ -13367,17 +13367,17 @@
         <f>'data'!$B$26</f>
       </c>
       <c r="B313" s="14" t="str">
-        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C313" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D313" s="18"/>
       <c r="E313" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F313" s="14" t="str">
-        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F314," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C314," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F315," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C315," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C318," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G313" s="14" t="str">
         <f>'data'!$B$24</f>
@@ -13386,17 +13386,17 @@
         <f>'data'!$B$73</f>
       </c>
       <c r="J313" s="14" t="str">
-        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K313" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L313" s="18"/>
       <c r="M313" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N313" s="14" t="str">
-        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L314)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N314," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J314," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K314," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L315)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N315," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J315," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K315," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L316)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N316," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J316," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K316," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L317)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N317," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J317," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K317," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L318)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N318," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J318," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K318," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O313" s="14" t="str">
         <f>'data'!$B$71</f>
@@ -13555,17 +13555,17 @@
         <f>'data'!$B$26</f>
       </c>
       <c r="B321" s="14" t="str">
-        <f>IF(UPPER(D322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C321" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D321" s="18"/>
       <c r="E321" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F321" s="14" t="str">
-        <f>IF(UPPER(D322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F322," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C322," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F323," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C323," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C326," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G321" s="14" t="str">
         <f>'data'!$B$25</f>
@@ -13574,17 +13574,17 @@
         <f>'data'!$B$73</f>
       </c>
       <c r="J321" s="14" t="str">
-        <f>IF(UPPER(L322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K321" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L321" s="18"/>
       <c r="M321" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N321" s="14" t="str">
-        <f>IF(UPPER(L322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L322)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N322," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J322," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K322," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L323)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N323," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J323," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K323," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L324)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N324," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J324," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K324," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L325)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N325," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J325," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K325," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L326)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N326," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J326," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K326," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O321" s="14" t="str">
         <f>'data'!$B$72</f>
@@ -14113,17 +14113,17 @@
         <f>'data'!$B$28</f>
       </c>
       <c r="B348" s="14" t="str">
-        <f>IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C348" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D348" s="18"/>
       <c r="E348" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F348" s="14" t="str">
-        <f>IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F349," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C349," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C350," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F351," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C351," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F352," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C352," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C353," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G348" s="14" t="str">
         <f>'data'!$B$27</f>
@@ -14132,17 +14132,17 @@
         <f>'data'!$B$75</f>
       </c>
       <c r="J348" s="14" t="str">
-        <f>IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K348" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L348" s="18"/>
       <c r="M348" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N348" s="14" t="str">
-        <f>IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L349)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N349," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J349," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K349," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L350)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N350," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J350," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K350," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L351)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N351," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J351," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K351," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L352)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N352," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J352," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K352," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L353)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N353," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J353," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K353," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O348" s="14" t="str">
         <f>'data'!$B$74</f>
@@ -14301,17 +14301,17 @@
         <f>'data'!$B$29</f>
       </c>
       <c r="B356" s="14" t="str">
-        <f>IF(UPPER(D357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C356" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D356" s="18"/>
       <c r="E356" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F356" s="14" t="str">
-        <f>IF(UPPER(D357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F357," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C357," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F358," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C358," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C361," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G356" s="14" t="str">
         <f>'data'!$B$27</f>
@@ -14320,17 +14320,17 @@
         <f>'data'!$B$76</f>
       </c>
       <c r="J356" s="14" t="str">
-        <f>IF(UPPER(L357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K356" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L356" s="18"/>
       <c r="M356" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N356" s="14" t="str">
-        <f>IF(UPPER(L357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L357)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N357," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J357," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K357," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L358)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N358," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J358," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K358," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L359)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N359," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J359," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K359," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L360)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N360," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J360," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K360," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L361)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N361," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J361," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K361," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O356" s="14" t="str">
         <f>'data'!$B$74</f>
@@ -14489,17 +14489,17 @@
         <f>'data'!$B$29</f>
       </c>
       <c r="B364" s="14" t="str">
-        <f>IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C364" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D364" s="18"/>
       <c r="E364" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F364" s="14" t="str">
-        <f>IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F365," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C365," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C366," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C369," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G364" s="14" t="str">
         <f>'data'!$B$28</f>
@@ -14508,17 +14508,17 @@
         <f>'data'!$B$76</f>
       </c>
       <c r="J364" s="14" t="str">
-        <f>IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K364" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L364" s="18"/>
       <c r="M364" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N364" s="14" t="str">
-        <f>IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L365)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N365," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J365," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K365," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L366)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N366," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J366," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K366," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L367)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N367," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J367," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K367," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L368)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N368," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J368," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K368," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L369)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N369," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J369," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K369," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O364" s="14" t="str">
         <f>'data'!$B$75</f>
@@ -15047,17 +15047,17 @@
         <f>'data'!$B$31</f>
       </c>
       <c r="B391" s="14" t="str">
-        <f>IF(UPPER(D392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C391" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D391" s="18"/>
       <c r="E391" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F391" s="14" t="str">
-        <f>IF(UPPER(D392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F392," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C392," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F393," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C393," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F394," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C394," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F395," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C395," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C396," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G391" s="14" t="str">
         <f>'data'!$B$30</f>
@@ -15066,17 +15066,17 @@
         <f>'data'!$B$78</f>
       </c>
       <c r="J391" s="14" t="str">
-        <f>IF(UPPER(L392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K391" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L391" s="18"/>
       <c r="M391" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N391" s="14" t="str">
-        <f>IF(UPPER(L392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L392)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N392," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J392," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K392," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L393)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N393," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J393," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K393," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L394)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N394," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J394," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K394," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L395)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N395," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J395," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K395," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L396)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N396," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J396," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K396," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O391" s="14" t="str">
         <f>'data'!$B$77</f>
@@ -15235,17 +15235,17 @@
         <f>'data'!$B$32</f>
       </c>
       <c r="B399" s="14" t="str">
-        <f>IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C399" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D399" s="18"/>
       <c r="E399" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F399" s="14" t="str">
-        <f>IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F400," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C400," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F401," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C401," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C404," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G399" s="14" t="str">
         <f>'data'!$B$30</f>
@@ -15254,17 +15254,17 @@
         <f>'data'!$B$79</f>
       </c>
       <c r="J399" s="14" t="str">
-        <f>IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K399" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L399" s="18"/>
       <c r="M399" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N399" s="14" t="str">
-        <f>IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L400)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N400," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J400," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K400," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L401)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N401," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J401," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K401," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L402)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N402," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J402," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K402," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L403)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N403," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J403," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K403," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L404)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N404," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J404," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K404," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O399" s="14" t="str">
         <f>'data'!$B$77</f>
@@ -15423,17 +15423,17 @@
         <f>'data'!$B$32</f>
       </c>
       <c r="B407" s="14" t="str">
-        <f>IF(UPPER(D408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C407" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D407" s="18"/>
       <c r="E407" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F407" s="14" t="str">
-        <f>IF(UPPER(D408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F408," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C408," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F409," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C409," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C412," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G407" s="14" t="str">
         <f>'data'!$B$31</f>
@@ -15442,17 +15442,17 @@
         <f>'data'!$B$79</f>
       </c>
       <c r="J407" s="14" t="str">
-        <f>IF(UPPER(L408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K407" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L407" s="18"/>
       <c r="M407" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N407" s="14" t="str">
-        <f>IF(UPPER(L408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L408)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N408," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J408," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K408," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L409)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N409," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J409," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K409," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L410)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N410," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J410," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K410," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L411)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N411," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J411," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K411," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L412)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N412," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J412," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K412," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O407" s="14" t="str">
         <f>'data'!$B$78</f>
@@ -15981,17 +15981,17 @@
         <f>'data'!$B$34</f>
       </c>
       <c r="B434" s="14" t="str">
-        <f>IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C434" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D434" s="18"/>
       <c r="E434" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F434" s="14" t="str">
-        <f>IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C435," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F436," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C436," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F437," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C437," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F438," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C438," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C439," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G434" s="14" t="str">
         <f>'data'!$B$33</f>
@@ -16000,17 +16000,17 @@
         <f>'data'!$B$81</f>
       </c>
       <c r="J434" s="14" t="str">
-        <f>IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K434" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L434" s="18"/>
       <c r="M434" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N434" s="14" t="str">
-        <f>IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L435)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N435," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J435," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K435," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L436)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N436," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J436," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K436," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L437)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N437," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J437," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K437," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L438)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N438," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J438," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K438," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L439)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N439," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J439," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K439," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O434" s="14" t="str">
         <f>'data'!$B$80</f>
@@ -16169,17 +16169,17 @@
         <f>'data'!$B$35</f>
       </c>
       <c r="B442" s="14" t="str">
-        <f>IF(UPPER(D443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C442" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D442" s="18"/>
       <c r="E442" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F442" s="14" t="str">
-        <f>IF(UPPER(D443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F443," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C443," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F444," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C444," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C447," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G442" s="14" t="str">
         <f>'data'!$B$33</f>
@@ -16188,17 +16188,17 @@
         <f>'data'!$B$82</f>
       </c>
       <c r="J442" s="14" t="str">
-        <f>IF(UPPER(L443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K442" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L442" s="18"/>
       <c r="M442" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N442" s="14" t="str">
-        <f>IF(UPPER(L443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L443)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N443," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J443," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K443," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L444)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N444," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J444," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K444," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L445)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N445," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J445," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K445," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L446)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N446," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J446," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K446," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L447)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N447," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J447," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K447," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O442" s="14" t="str">
         <f>'data'!$B$80</f>
@@ -16357,17 +16357,17 @@
         <f>'data'!$B$35</f>
       </c>
       <c r="B450" s="14" t="str">
-        <f>IF(UPPER(D451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C450" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D450" s="18"/>
       <c r="E450" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F450" s="14" t="str">
-        <f>IF(UPPER(D451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F451," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C451," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F452," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C452," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C455," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G450" s="14" t="str">
         <f>'data'!$B$34</f>
@@ -16376,17 +16376,17 @@
         <f>'data'!$B$82</f>
       </c>
       <c r="J450" s="14" t="str">
-        <f>IF(UPPER(L451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K450" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L450" s="18"/>
       <c r="M450" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N450" s="14" t="str">
-        <f>IF(UPPER(L451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L451)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N451," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J451," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K451," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L452)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N452," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J452," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K452," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L453)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N453," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J453," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K453," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L454)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N454," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J454," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K454," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L455)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N455," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J455," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K455," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O450" s="14" t="str">
         <f>'data'!$B$81</f>
@@ -16915,17 +16915,17 @@
         <f>'data'!$B$37</f>
       </c>
       <c r="B477" s="14" t="str">
-        <f>IF(UPPER(D478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C477" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D477" s="18"/>
       <c r="E477" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F477" s="14" t="str">
-        <f>IF(UPPER(D478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F478," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C478," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F479," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C479," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F480," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C480," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F481," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C481," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C482," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G477" s="14" t="str">
         <f>'data'!$B$36</f>
@@ -16934,17 +16934,17 @@
         <f>'data'!$B$84</f>
       </c>
       <c r="J477" s="14" t="str">
-        <f>IF(UPPER(L478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K477" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L477" s="18"/>
       <c r="M477" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N477" s="14" t="str">
-        <f>IF(UPPER(L478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L478)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N478," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J478," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K478," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L479)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N479," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J479," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K479," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L480)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N480," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J480," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K480," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L481)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N481," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J481," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K481," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L482)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N482," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J482," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K482," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O477" s="14" t="str">
         <f>'data'!$B$83</f>
@@ -17103,17 +17103,17 @@
         <f>'data'!$B$38</f>
       </c>
       <c r="B485" s="14" t="str">
-        <f>IF(UPPER(D486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C485" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D485" s="18"/>
       <c r="E485" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F485" s="14" t="str">
-        <f>IF(UPPER(D486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F486," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C486," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F487," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C487," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C490," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G485" s="14" t="str">
         <f>'data'!$B$36</f>
@@ -17122,17 +17122,17 @@
         <f>'data'!$B$85</f>
       </c>
       <c r="J485" s="14" t="str">
-        <f>IF(UPPER(L486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K485" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L485" s="18"/>
       <c r="M485" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N485" s="14" t="str">
-        <f>IF(UPPER(L486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L486)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N486," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J486," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K486," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L487)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N487," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J487," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K487," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L488)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N488," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J488," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K488," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L489)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N489," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J489," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K489," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L490)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N490," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J490," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K490," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O485" s="14" t="str">
         <f>'data'!$B$83</f>
@@ -17291,17 +17291,17 @@
         <f>'data'!$B$38</f>
       </c>
       <c r="B493" s="14" t="str">
-        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C493" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D493" s="18"/>
       <c r="E493" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F493" s="14" t="str">
-        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F494," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C494," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F495," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C495," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C498," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G493" s="14" t="str">
         <f>'data'!$B$37</f>
@@ -17310,17 +17310,17 @@
         <f>'data'!$B$85</f>
       </c>
       <c r="J493" s="14" t="str">
-        <f>IF(UPPER(L494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K493" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L493" s="18"/>
       <c r="M493" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N493" s="14" t="str">
-        <f>IF(UPPER(L494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L494)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N494," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J494," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K494," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L495)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N495," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J495," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K495," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L496)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N496," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J496," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K496," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L497)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N497," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J497," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K497," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L498)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N498," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J498," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K498," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O493" s="14" t="str">
         <f>'data'!$B$84</f>
@@ -17849,17 +17849,17 @@
         <f>'data'!$B$40</f>
       </c>
       <c r="B520" s="14" t="str">
-        <f>IF(UPPER(D521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C520" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D520" s="18"/>
       <c r="E520" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F520" s="14" t="str">
-        <f>IF(UPPER(D521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F521," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C521," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F522," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C522," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F523," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C523," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F524," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C524," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C525," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G520" s="14" t="str">
         <f>'data'!$B$39</f>
@@ -17868,17 +17868,17 @@
         <f>'data'!$B$87</f>
       </c>
       <c r="J520" s="14" t="str">
-        <f>IF(UPPER(L521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K520" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L520" s="18"/>
       <c r="M520" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N520" s="14" t="str">
-        <f>IF(UPPER(L521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L521)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N521," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J521," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K521," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L522)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N522," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J522," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K522," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L523)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N523," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J523," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K523," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L524)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N524," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J524," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K524," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L525)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N525," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J525," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K525," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O520" s="14" t="str">
         <f>'data'!$B$86</f>
@@ -18037,17 +18037,17 @@
         <f>'data'!$B$41</f>
       </c>
       <c r="B528" s="14" t="str">
-        <f>IF(UPPER(D529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C528" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D528" s="18"/>
       <c r="E528" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F528" s="14" t="str">
-        <f>IF(UPPER(D529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F529," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C529," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F530," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C530," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C533," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G528" s="14" t="str">
         <f>'data'!$B$39</f>
@@ -18056,17 +18056,17 @@
         <f>'data'!$B$88</f>
       </c>
       <c r="J528" s="14" t="str">
-        <f>IF(UPPER(L529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K528" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L528" s="18"/>
       <c r="M528" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N528" s="14" t="str">
-        <f>IF(UPPER(L529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L529)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N529," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J529," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K529," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L530)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N530," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J530," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K530," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L531)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N531," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J531," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K531," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L532)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N532," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J532," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K532," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L533)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N533," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J533," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K533," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O528" s="14" t="str">
         <f>'data'!$B$86</f>
@@ -18225,17 +18225,17 @@
         <f>'data'!$B$41</f>
       </c>
       <c r="B536" s="14" t="str">
-        <f>IF(UPPER(D537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C536" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D536" s="18"/>
       <c r="E536" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F536" s="14" t="str">
-        <f>IF(UPPER(D537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F537," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C537," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F538," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C538," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C541," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G536" s="14" t="str">
         <f>'data'!$B$40</f>
@@ -18244,17 +18244,17 @@
         <f>'data'!$B$88</f>
       </c>
       <c r="J536" s="14" t="str">
-        <f>IF(UPPER(L537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K536" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L536" s="18"/>
       <c r="M536" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N536" s="14" t="str">
-        <f>IF(UPPER(L537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L537)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N537," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J537," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K537," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L538)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N538," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J538," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K538," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L539)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N539," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J539," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K539," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L540)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N540," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J540," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K540," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L541)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N541," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J541," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K541," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O536" s="14" t="str">
         <f>'data'!$B$87</f>
@@ -18783,17 +18783,17 @@
         <f>'data'!$B$43</f>
       </c>
       <c r="B563" s="14" t="str">
-        <f>IF(UPPER(D564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C563" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D563" s="18"/>
       <c r="E563" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F563" s="14" t="str">
-        <f>IF(UPPER(D564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F564," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C564," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F565," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C565," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F566," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C566," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F567," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C567," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C568," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G563" s="14" t="str">
         <f>'data'!$B$42</f>
@@ -18802,17 +18802,17 @@
         <f>'data'!$B$90</f>
       </c>
       <c r="J563" s="14" t="str">
-        <f>IF(UPPER(L564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K563" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L563" s="18"/>
       <c r="M563" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N563" s="14" t="str">
-        <f>IF(UPPER(L564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L564)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N564," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J564," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K564," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L565)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N565," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J565," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K565," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L566)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N566," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J566," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K566," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L567)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N567," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J567," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K567," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L568)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N568," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J568," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K568," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O563" s="14" t="str">
         <f>'data'!$B$89</f>
@@ -18971,17 +18971,17 @@
         <f>'data'!$B$44</f>
       </c>
       <c r="B571" s="14" t="str">
-        <f>IF(UPPER(D572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C571" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D571" s="18"/>
       <c r="E571" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F571" s="14" t="str">
-        <f>IF(UPPER(D572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F572," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C572," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F573," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C573," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C576," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G571" s="14" t="str">
         <f>'data'!$B$42</f>
@@ -18990,17 +18990,17 @@
         <f>'data'!$B$91</f>
       </c>
       <c r="J571" s="14" t="str">
-        <f>IF(UPPER(L572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K571" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L571" s="18"/>
       <c r="M571" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N571" s="14" t="str">
-        <f>IF(UPPER(L572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L572)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N572," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J572," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K572," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L573)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N573," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J573," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K573," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L574)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N574," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J574," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K574," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L575)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N575," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J575," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K575," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L576)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N576," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J576," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K576," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O571" s="14" t="str">
         <f>'data'!$B$89</f>
@@ -19159,17 +19159,17 @@
         <f>'data'!$B$44</f>
       </c>
       <c r="B579" s="14" t="str">
-        <f>IF(UPPER(D580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C579" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D579" s="18"/>
       <c r="E579" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F579" s="14" t="str">
-        <f>IF(UPPER(D580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F580," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C580," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F581," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C581," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C584," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G579" s="14" t="str">
         <f>'data'!$B$43</f>
@@ -19178,17 +19178,17 @@
         <f>'data'!$B$91</f>
       </c>
       <c r="J579" s="14" t="str">
-        <f>IF(UPPER(L580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K579" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L579" s="18"/>
       <c r="M579" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N579" s="14" t="str">
-        <f>IF(UPPER(L580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L580)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N580," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J580," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K580," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L581)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N581," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J581," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K581," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L582)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N582," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J582," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K582," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L583)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N583," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J583," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K583," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L584)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N584," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J584," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K584," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O579" s="14" t="str">
         <f>'data'!$B$90</f>
@@ -19717,17 +19717,17 @@
         <f>'data'!$B$46</f>
       </c>
       <c r="B606" s="14" t="str">
-        <f>IF(UPPER(D607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C606" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D606" s="18"/>
       <c r="E606" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F606" s="14" t="str">
-        <f>IF(UPPER(D607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F607," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C607," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F608," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C608," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F609," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C609," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F610," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C610," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C611," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G606" s="14" t="str">
         <f>'data'!$B$45</f>
@@ -19736,17 +19736,17 @@
         <f>'data'!$B$93</f>
       </c>
       <c r="J606" s="14" t="str">
-        <f>IF(UPPER(L607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K606" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L606" s="18"/>
       <c r="M606" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N606" s="14" t="str">
-        <f>IF(UPPER(L607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L607)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N607," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J607," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K607," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L608)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N608," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J608," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K608," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L609)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N609," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J609," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K609," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L610)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N610," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J610," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K610," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L611)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N611," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J611," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K611," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O606" s="14" t="str">
         <f>'data'!$B$92</f>
@@ -19892,17 +19892,17 @@
         <f>'data'!$B$47</f>
       </c>
       <c r="B614" s="14" t="str">
-        <f>IF(UPPER(D615)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D616)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D615)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D616)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C614" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D614" s="18"/>
       <c r="E614" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F614" s="14" t="str">
-        <f>IF(UPPER(D615)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D616)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D615)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F615," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B615," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C615," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D616)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F616," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B616," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C616," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D617)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F617," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B617," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C617," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D618)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F618," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B618," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C618," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D619)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F619," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B619," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C619," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G614" s="14" t="str">
         <f>'data'!$B$45</f>
@@ -19993,17 +19993,17 @@
         <f>'data'!$B$47</f>
       </c>
       <c r="B622" s="14" t="str">
-        <f>IF(UPPER(D623)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D624)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D623)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D624)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C622" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D622" s="18"/>
       <c r="E622" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F622" s="14" t="str">
-        <f>IF(UPPER(D623)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D624)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D623)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F623," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B623," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C623," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D624)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F624," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B624," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C624," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D625)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F625," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B625," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C625," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D626)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F626," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B626," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C626," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D627)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F627," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B627," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C627," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G622" s="14" t="str">
         <f>'data'!$B$46</f>
@@ -20419,17 +20419,17 @@
         <f>'data'!$B$49</f>
       </c>
       <c r="B649" s="14" t="str">
-        <f>IF(UPPER(D650)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D651)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D652)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D653)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D654)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D650)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D651)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D652)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D653)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D654)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C649" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D649" s="18"/>
       <c r="E649" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F649" s="14" t="str">
-        <f>IF(UPPER(D650)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D651)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D652)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D653)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D654)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D650)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F650," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B650," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C650," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D651)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F651," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B651," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C651," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D652)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F652," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B652," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C652," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D653)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F653," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B653," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C653," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D654)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F654," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B654," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C654," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G649" s="14" t="str">
         <f>'data'!$B$48</f>
@@ -20969,17 +20969,17 @@
         <v>348</v>
       </c>
       <c r="B12" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F12" s="14" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="14" t="s">
         <v>348</v>
@@ -20988,17 +20988,17 @@
         <v>348</v>
       </c>
       <c r="J12" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N12" s="14" t="str">
-        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O12" s="14" t="s">
         <v>348</v>
@@ -21253,17 +21253,17 @@
         <v>348</v>
       </c>
       <c r="B28" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F28" s="14" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G28" s="14" t="s">
         <v>348</v>
@@ -21272,17 +21272,17 @@
         <v>348</v>
       </c>
       <c r="J28" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L28" s="14"/>
       <c r="M28" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N28" s="14" t="str">
-        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O28" s="14" t="s">
         <v>348</v>
@@ -21537,17 +21537,17 @@
         <v>348</v>
       </c>
       <c r="B44" s="14" t="str">
-        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C44" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F44" s="14" t="str">
-        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G44" s="14" t="s">
         <v>348</v>
@@ -21556,17 +21556,17 @@
         <v>348</v>
       </c>
       <c r="J44" s="14" t="str">
-        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K44" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L44" s="14"/>
       <c r="M44" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N44" s="14" t="str">
-        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O44" s="14" t="s">
         <v>348</v>
@@ -21821,17 +21821,17 @@
         <v>348</v>
       </c>
       <c r="B60" s="14" t="str">
-        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C60" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F60" s="14" t="str">
-        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G60" s="14" t="s">
         <v>348</v>
@@ -21840,17 +21840,17 @@
         <v>348</v>
       </c>
       <c r="J60" s="14" t="str">
-        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K60" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L60" s="14"/>
       <c r="M60" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N60" s="14" t="str">
-        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O60" s="14" t="s">
         <v>348</v>
@@ -22105,17 +22105,17 @@
         <v>348</v>
       </c>
       <c r="B76" s="14" t="str">
-        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F76" s="14" t="str">
-        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C70," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G76" s="14" t="s">
         <v>348</v>
@@ -22124,17 +22124,17 @@
         <v>348</v>
       </c>
       <c r="J76" s="14" t="str">
-        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L76" s="14"/>
       <c r="M76" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N76" s="14" t="str">
-        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L69)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N69," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J69," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K69," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L70)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N70," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J70," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K70," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L71)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N71," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J71," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K71," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L72)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N72," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J72," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K72," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L73)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N73," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J73," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K73," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O76" s="14" t="s">
         <v>348</v>
@@ -22389,17 +22389,17 @@
         <v>348</v>
       </c>
       <c r="B92" s="14" t="str">
-        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C92" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D92" s="14"/>
       <c r="E92" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F92" s="14" t="str">
-        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C87," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C89," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G92" s="14" t="s">
         <v>348</v>
@@ -22408,17 +22408,17 @@
         <v>348</v>
       </c>
       <c r="J92" s="14" t="str">
-        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K92" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L92" s="14"/>
       <c r="M92" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N92" s="14" t="str">
-        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L85)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N85," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J85," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K85," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L86)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N86," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J86," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K86," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L87)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N87," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J87," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K87," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L88)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N88," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J88," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K88," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L89)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N89," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J89," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K89," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O92" s="14" t="s">
         <v>348</v>
@@ -22673,17 +22673,17 @@
         <v>348</v>
       </c>
       <c r="B108" s="14" t="str">
-        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F108" s="14" t="str">
-        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G108" s="14" t="s">
         <v>348</v>
@@ -22692,17 +22692,17 @@
         <v>348</v>
       </c>
       <c r="J108" s="14" t="str">
-        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L108" s="14"/>
       <c r="M108" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N108" s="14" t="str">
-        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L101)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N101," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J101," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K101," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L102)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N102," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J102," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K102," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L103)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N103," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J103," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K103," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L104)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N104," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J104," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K104," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L105)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N105," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J105," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K105," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O108" s="14" t="s">
         <v>348</v>
@@ -22957,17 +22957,17 @@
         <v>348</v>
       </c>
       <c r="B124" s="14" t="str">
-        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C124" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D124" s="14"/>
       <c r="E124" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F124" s="14" t="str">
-        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G124" s="14" t="s">
         <v>348</v>
@@ -22976,17 +22976,17 @@
         <v>348</v>
       </c>
       <c r="J124" s="14" t="str">
-        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K124" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="L124" s="14"/>
       <c r="M124" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N124" s="14" t="str">
-        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L117)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N117," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J117," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K117," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L118)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N118," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J118," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K118," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L119)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N119," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J119," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K119," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L120)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N120," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J120," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K120," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L121)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N121," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J121," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K121," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="O124" s="14" t="s">
         <v>348</v>
@@ -23241,17 +23241,17 @@
         <v>348</v>
       </c>
       <c r="B140" s="14" t="str">
-        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C140" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D140" s="14"/>
       <c r="E140" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F140" s="14" t="str">
-        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F133," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C133," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C137," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G140" s="14" t="s">
         <v>348</v>
@@ -23260,17 +23260,17 @@
         <v>348</v>
       </c>
       <c r="J140" s="14" t="str">
-        <f>IF(UPPER(L133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(L133)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N133," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L134)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N134," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L135)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M135," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N135," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L136)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M136," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N136," ",""),"0",""),"-",""))),1,0))+IF(UPPER(L137)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M137," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N137," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="K140" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K134," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K135," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K136," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J137," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K137," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K133," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J134," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K13